--- a/lib/davinci_crd_test_kit/requirements/hl7.fhir.us.davinci-crd_2.2.1_requirements.xlsx
+++ b/lib/davinci_crd_test_kit/requirements/hl7.fhir.us.davinci-crd_2.2.1_requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-crd-test-kit/lib/davinci_crd_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D512B22D-317F-B246-A23A-55DA2C77A20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7AD7FE-7657-FE43-8930-18452B3BCEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="760" windowWidth="34240" windowHeight="21260" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Column Data" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$U$435</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$U$436</definedName>
     <definedName name="EXPLODE" localSheetId="0">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="EXPLODE">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="FIND_DUPLICATES" localSheetId="0">_xlfn.LAMBDA(_xlpm.test_word,_xlpm.test_key,_xlpm.words,_xlpm.keys,_xlpm.threshold, _xlfn.LET(_xlpm.duplist,_xlfn._xlws.FILTER(_xlpm.keys,_xlfn.BYROW(_xlpm.words, _xlfn.LAMBDA(_xlpm.word, Info!HAMDIST(INDEX(_xlpm.word,1,1), _xlpm.test_word)&lt;_xlpm.threshold))),_xlfn.SINGLE(_xlfn._xlws.FILTER(_xlpm.duplist,_xlpm.duplist&lt;&gt;_xlpm.test_key,""))))</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="845">
   <si>
     <r>
       <rPr>
@@ -2082,13 +2082,7 @@
     <t>As well, cards **SHOULD** include the associated-resource extension to allow computable linkage.</t>
   </si>
   <si>
-    <t>dev-26</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-crd/2.2.1/en/deviations.html#ci-c-dev-26</t>
-  </si>
-  <si>
-    <t>CRD clients **SHALL** only invoke hooks on payer services where the patient record indicates active coverage with the payer associated with the service and where there is no recorded indication the patient intends to bypass insurance coverage (i.e. the service or product is not flagged as 'patient-pay').</t>
   </si>
   <si>
     <t>dev-27</t>
@@ -3923,6 +3917,18 @@
 - HRex: [Privacy &amp; Security](http://hl7.org/fhir/us/davinci-hrex/1.2.0/security.html)
 - CDS Hooks: [Security &amp; Safety](http://cds-hooks.hl7.org/2026Jan/index.html#security-and-safety)
 - SMART on FHIR: [SMART App Launch](http://www.hl7.org/fhir/smart-app-launch)</t>
+  </si>
+  <si>
+    <t>dev-26-A</t>
+  </si>
+  <si>
+    <t>dev-26-B</t>
+  </si>
+  <si>
+    <t>CRD clients **SHALL** only invoke hooks on payer services where the patient record indicates active coverage with the payer associated with the service</t>
+  </si>
+  <si>
+    <t>CRD clients **SHALL** only invoke hooks on payer services where ... there is no recorded indication the patient intends to bypass insurance coverage (i.e. the service or product is not flagged as 'patient-pay').</t>
   </si>
 </sst>
 </file>
@@ -4835,7 +4841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
-  <dimension ref="A1:AF435"/>
+  <dimension ref="A1:AF436"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="25"/>
@@ -4918,7 +4924,7 @@
         <v>23</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T1" s="39" t="s">
         <v>24</v>
@@ -4961,7 +4967,7 @@
       </c>
       <c r="Q2" s="27"/>
       <c r="R2" s="27" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="S2" s="27" t="s">
         <v>68</v>
@@ -5077,7 +5083,7 @@
         <v>93</v>
       </c>
       <c r="R6" s="27" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="S6" s="27" t="s">
         <v>68</v>
@@ -5129,10 +5135,10 @@
         <v>93</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="S8" s="27" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -5207,7 +5213,7 @@
         <v>82</v>
       </c>
       <c r="S11" s="27" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="119" x14ac:dyDescent="0.2">
@@ -5305,7 +5311,7 @@
         <v>84</v>
       </c>
       <c r="S15" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="16" spans="1:32" ht="68" x14ac:dyDescent="0.2">
@@ -5380,10 +5386,10 @@
         <v>93</v>
       </c>
       <c r="R18" s="27" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="S18" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="68" x14ac:dyDescent="0.2">
@@ -5950,7 +5956,7 @@
         <v>97</v>
       </c>
       <c r="R42" s="27" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="85" x14ac:dyDescent="0.2">
@@ -5976,7 +5982,7 @@
         <v>97</v>
       </c>
       <c r="R43" s="27" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="51" x14ac:dyDescent="0.2">
@@ -6002,7 +6008,7 @@
         <v>97</v>
       </c>
       <c r="R44" s="27" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="85" x14ac:dyDescent="0.2">
@@ -6051,15 +6057,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A47" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="B47" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="B47" s="32" t="s">
-        <v>231</v>
-      </c>
       <c r="C47" s="25" t="s">
-        <v>232</v>
+        <v>843</v>
       </c>
       <c r="D47" s="25" t="s">
         <v>27</v>
@@ -6079,16 +6085,16 @@
     </row>
     <row r="48" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A48" s="25" t="s">
-        <v>233</v>
+        <v>842</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>235</v>
+        <v>844</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>63</v>
@@ -6099,42 +6105,42 @@
       <c r="P48" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="R48" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" s="25" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E49" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G49" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R49" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A50" s="25" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>27</v>
@@ -6143,30 +6149,27 @@
         <v>63</v>
       </c>
       <c r="G50" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="27" t="s">
         <v>93</v>
       </c>
       <c r="R50" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="S50" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A51" s="25" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>63</v>
@@ -6177,45 +6180,48 @@
       <c r="P51" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="R51" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="S51" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="25" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G52" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R52" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" s="25" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E53" s="25" t="s">
         <v>63</v>
@@ -6226,19 +6232,22 @@
       <c r="P53" s="27" t="s">
         <v>93</v>
       </c>
+      <c r="R53" s="27" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="54" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A54" s="25" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E54" s="25" t="s">
         <v>63</v>
@@ -6249,166 +6258,160 @@
       <c r="P54" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R54" s="27" t="s">
+    </row>
+    <row r="55" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A55" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G55" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P55" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R55" s="27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A55" s="25" t="s">
+    <row r="56" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A56" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="C56" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B55" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="D55" s="25" t="s">
+      <c r="D56" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="25" t="s">
+      <c r="E56" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="G55" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P55" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A56" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="B56" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="25" t="s">
-        <v>64</v>
-      </c>
       <c r="G56" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P56" s="27" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A57" s="25" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G57" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" s="25" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G58" s="25" t="b">
         <v>1</v>
       </c>
       <c r="P58" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A59" s="25" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D59" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G59" s="25" t="b">
         <v>1</v>
       </c>
       <c r="P59" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A60" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G60" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P60" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A61" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="C61" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="B60" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G60" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P60" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="R60" s="27" t="s">
-        <v>797</v>
-      </c>
-      <c r="S60" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A61" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="B61" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>273</v>
-      </c>
       <c r="D61" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E61" s="25" t="s">
         <v>63</v>
@@ -6419,65 +6422,71 @@
       <c r="P61" s="27" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="R61" s="27" t="s">
+        <v>795</v>
+      </c>
+      <c r="S61" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A62" s="25" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E62" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G62" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A63" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G63" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P62" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A63" s="25" t="s">
+      <c r="P63" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A64" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="C64" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="B63" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G63" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P63" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A64" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="B64" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>282</v>
-      </c>
       <c r="D64" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E64" s="25" t="s">
         <v>64</v>
@@ -6486,21 +6495,21 @@
         <v>0</v>
       </c>
       <c r="P64" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="25" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B65" s="32" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>64</v>
@@ -6509,64 +6518,64 @@
         <v>0</v>
       </c>
       <c r="P65" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A66" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" s="27" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A67" s="25" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A66" s="25" t="s">
+      <c r="B67" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C67" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="B66" s="32" t="s">
+      <c r="D67" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G67" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P67" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A68" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="C66" s="25" t="s">
+      <c r="B68" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="D66" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G66" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P66" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="25" t="s">
+      <c r="C68" s="25" t="s">
         <v>290</v>
-      </c>
-      <c r="B67" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G67" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P67" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A68" s="25" t="s">
-        <v>293</v>
-      </c>
-      <c r="B68" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="C68" s="25" t="s">
-        <v>295</v>
       </c>
       <c r="D68" s="25" t="s">
         <v>27</v>
@@ -6575,21 +6584,21 @@
         <v>64</v>
       </c>
       <c r="G68" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A69" s="25" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D69" s="25" t="s">
         <v>27</v>
@@ -6604,38 +6613,38 @@
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="D70" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G70" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P70" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="A71" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="C71" s="25" t="s">
         <v>299</v>
-      </c>
-      <c r="B70" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G70" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P70" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A71" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="B71" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>304</v>
       </c>
       <c r="D71" s="25" t="s">
         <v>28</v>
@@ -6644,96 +6653,90 @@
         <v>63</v>
       </c>
       <c r="G71" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="119" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="25" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E72" s="25" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="G72" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" ht="119" x14ac:dyDescent="0.2">
       <c r="A73" s="25" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E73" s="25" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="G73" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" s="27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A74" s="25" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E74" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G74" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R74" s="27" t="s">
-        <v>822</v>
-      </c>
-      <c r="S74" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A75" s="25" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D75" s="25" t="s">
         <v>27</v>
@@ -6745,27 +6748,27 @@
         <v>0</v>
       </c>
       <c r="P75" s="27" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R75" s="27" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="S75" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A76" s="25" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E76" s="25" t="s">
         <v>63</v>
@@ -6776,19 +6779,25 @@
       <c r="P76" s="27" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="R76" s="27" t="s">
+        <v>806</v>
+      </c>
+      <c r="S76" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A77" s="25" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E77" s="25" t="s">
         <v>63</v>
@@ -6799,57 +6808,51 @@
       <c r="P77" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="R77" s="27" t="s">
-        <v>809</v>
-      </c>
-      <c r="S77" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A78" s="25" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D78" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="G78" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P78" s="27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="R78" s="27" t="s">
-        <v>823</v>
+        <v>807</v>
       </c>
       <c r="S78" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="136" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A79" s="25" t="s">
-        <v>825</v>
+        <v>321</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D79" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="G79" s="25" t="b">
         <v>0</v>
@@ -6858,21 +6861,21 @@
         <v>93</v>
       </c>
       <c r="R79" s="27" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="S79" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A80" s="25" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>826</v>
+        <v>325</v>
       </c>
       <c r="D80" s="25" t="s">
         <v>27</v>
@@ -6887,7 +6890,7 @@
         <v>93</v>
       </c>
       <c r="R80" s="27" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="S80" s="27" t="s">
         <v>68</v>
@@ -6895,39 +6898,45 @@
     </row>
     <row r="81" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A81" s="25" t="s">
+        <v>825</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>824</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G81" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R81" s="27" t="s">
+        <v>837</v>
+      </c>
+      <c r="S81" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A82" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="C82" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="B81" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D81" s="25" t="s">
+      <c r="D82" s="25" t="s">
         <v>26</v>
-      </c>
-      <c r="E81" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G81" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P81" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A82" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B82" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>28</v>
       </c>
       <c r="E82" s="25" t="s">
         <v>64</v>
@@ -6939,15 +6948,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D83" s="25" t="s">
         <v>28</v>
@@ -6956,24 +6965,24 @@
         <v>64</v>
       </c>
       <c r="G83" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>64</v>
@@ -6987,39 +6996,39 @@
     </row>
     <row r="85" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E85" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G85" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P85" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A86" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C86" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="B85" s="32" t="s">
-        <v>341</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>342</v>
-      </c>
-      <c r="D85" s="25" t="s">
+      <c r="D86" s="25" t="s">
         <v>29</v>
-      </c>
-      <c r="E85" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G85" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P85" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A86" s="25" t="s">
-        <v>343</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>344</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="D86" s="25" t="s">
-        <v>27</v>
       </c>
       <c r="E86" s="25" t="s">
         <v>63</v>
@@ -7030,28 +7039,22 @@
       <c r="P86" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="R86" s="27" t="s">
-        <v>840</v>
-      </c>
-      <c r="S86" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A87" s="25" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G87" s="25" t="b">
         <v>0</v>
@@ -7059,91 +7062,97 @@
       <c r="P87" s="27" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="88" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="R87" s="27" t="s">
+        <v>838</v>
+      </c>
+      <c r="S87" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A88" s="25" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="G88" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P88" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R88" s="27" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="25" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D89" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="G89" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P89" s="27" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="R89" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A90" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D90" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G90" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P90" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A91" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="B91" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="C91" s="25" t="s">
         <v>355</v>
       </c>
-      <c r="B90" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="D90" s="25" t="s">
+      <c r="D91" s="25" t="s">
         <v>28</v>
-      </c>
-      <c r="E90" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G90" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P90" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A91" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="B91" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>359</v>
-      </c>
-      <c r="D91" s="25" t="s">
-        <v>27</v>
       </c>
       <c r="E91" s="25" t="s">
         <v>63</v>
@@ -7154,22 +7163,19 @@
       <c r="P91" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R91" s="27" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A92" s="25" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E92" s="25" t="s">
         <v>63</v>
@@ -7180,19 +7186,22 @@
       <c r="P92" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="93" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="R92" s="27" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
-        <v>799</v>
+        <v>358</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>798</v>
+        <v>359</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E93" s="25" t="s">
         <v>63</v>
@@ -7203,22 +7212,16 @@
       <c r="P93" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R93" s="27" t="s">
-        <v>810</v>
-      </c>
-      <c r="S93" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A94" s="25" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="D94" s="25" t="s">
         <v>27</v>
@@ -7233,145 +7236,145 @@
         <v>93</v>
       </c>
       <c r="R94" s="27" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="S94" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A95" s="25" t="s">
-        <v>363</v>
+        <v>798</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>366</v>
+        <v>810</v>
       </c>
       <c r="D95" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="G95" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P95" s="27" t="s">
-        <v>365</v>
+        <v>93</v>
       </c>
       <c r="R95" s="27" t="s">
-        <v>65</v>
+        <v>809</v>
+      </c>
+      <c r="S95" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>362</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="D96" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E96" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G96" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P96" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="R96" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A97" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="C97" s="25" t="s">
         <v>367</v>
       </c>
-      <c r="B96" s="32" t="s">
+      <c r="D97" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E97" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="G97" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P97" s="27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A98" s="25" t="s">
         <v>368</v>
       </c>
-      <c r="C96" s="25" t="s">
+      <c r="B98" s="32" t="s">
         <v>369</v>
       </c>
-      <c r="D96" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E96" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="G96" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P96" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A97" s="25" t="s">
+      <c r="C98" s="25" t="s">
         <v>370</v>
-      </c>
-      <c r="B97" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="C97" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="D97" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E97" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G97" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P97" s="27" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A98" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="B98" s="32" t="s">
-        <v>374</v>
-      </c>
-      <c r="C98" s="25" t="s">
-        <v>375</v>
       </c>
       <c r="D98" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G98" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P98" s="27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A99" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="D99" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E99" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="G98" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P98" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A99" s="25" t="s">
+      <c r="G99" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P99" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A100" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="C100" s="25" t="s">
         <v>376</v>
-      </c>
-      <c r="B99" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>378</v>
-      </c>
-      <c r="D99" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E99" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G99" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P99" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="R99" s="27" t="s">
-        <v>829</v>
-      </c>
-      <c r="S99" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A100" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="B100" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="C100" s="25" t="s">
-        <v>381</v>
       </c>
       <c r="D100" s="25" t="s">
         <v>27</v>
@@ -7383,24 +7386,24 @@
         <v>0</v>
       </c>
       <c r="P100" s="27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="R100" s="27" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="S100" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" s="25" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D101" s="25" t="s">
         <v>27</v>
@@ -7415,24 +7418,24 @@
         <v>93</v>
       </c>
       <c r="R101" s="27" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="S101" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="25" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B102" s="32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E102" s="25" t="s">
         <v>63</v>
@@ -7443,48 +7446,51 @@
       <c r="P102" s="27" t="s">
         <v>93</v>
       </c>
+      <c r="R102" s="27" t="s">
+        <v>812</v>
+      </c>
+      <c r="S102" s="27" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="103" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A103" s="25" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B103" s="32" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E103" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G103" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P103" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R103" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="25" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D104" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G104" s="25" t="b">
         <v>1</v>
@@ -7492,25 +7498,28 @@
       <c r="P104" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="105" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="R104" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A105" s="25" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="G105" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P105" s="27" t="s">
         <v>93</v>
@@ -7518,71 +7527,68 @@
     </row>
     <row r="106" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A106" s="25" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E106" s="25" t="s">
         <v>137</v>
       </c>
       <c r="G106" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P106" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A107" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C107" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E107" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G107" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P106" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="107" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A107" s="25" t="s">
+      <c r="P107" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A108" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="C108" s="25" t="s">
         <v>398</v>
       </c>
-      <c r="B107" s="32" t="s">
-        <v>399</v>
-      </c>
-      <c r="C107" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="D107" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E107" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G107" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P107" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="R107" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A108" s="25" t="s">
-        <v>401</v>
-      </c>
-      <c r="B108" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>403</v>
-      </c>
       <c r="D108" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E108" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G108" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P108" s="27" t="s">
         <v>189</v>
@@ -7593,36 +7599,39 @@
     </row>
     <row r="109" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A109" s="25" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G109" s="25" t="b">
         <v>1</v>
       </c>
       <c r="P109" s="27" t="s">
-        <v>93</v>
+        <v>189</v>
+      </c>
+      <c r="R109" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="110" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A110" s="25" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D110" s="25" t="s">
         <v>27</v>
@@ -7637,38 +7646,38 @@
         <v>93</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A111" s="25" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B111" s="32" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G111" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" s="27" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="112" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="25" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D112" s="25" t="s">
         <v>26</v>
@@ -7677,7 +7686,7 @@
         <v>63</v>
       </c>
       <c r="G112" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112" s="27" t="s">
         <v>189</v>
@@ -7685,65 +7694,65 @@
     </row>
     <row r="113" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="25" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C113" s="25" t="s">
+        <v>413</v>
+      </c>
+      <c r="D113" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G113" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P113" s="27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A114" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="C114" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="D113" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E113" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G113" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P113" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A114" s="25" t="s">
-        <v>418</v>
-      </c>
-      <c r="B114" s="32" t="s">
-        <v>419</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>420</v>
-      </c>
       <c r="D114" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E114" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G114" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" s="27" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="115" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A115" s="25" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B115" s="32" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D115" s="25" t="s">
         <v>26</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G115" s="25" t="b">
         <v>1</v>
@@ -7752,90 +7761,90 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A116" s="25" t="s">
+        <v>419</v>
+      </c>
+      <c r="B116" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="D116" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G116" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P116" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="A117" s="25" t="s">
+        <v>422</v>
+      </c>
+      <c r="B117" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="C117" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="B116" s="32" t="s">
+      <c r="D117" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E117" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G117" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P117" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A118" s="25" t="s">
         <v>425</v>
       </c>
-      <c r="C116" s="25" t="s">
+      <c r="B118" s="32" t="s">
         <v>426</v>
       </c>
-      <c r="D116" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E116" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G116" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P116" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A117" s="25" t="s">
+      <c r="C118" s="25" t="s">
         <v>427</v>
       </c>
-      <c r="B117" s="32" t="s">
-        <v>428</v>
-      </c>
-      <c r="C117" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="D117" s="25" t="s">
+      <c r="D118" s="25" t="s">
         <v>26</v>
-      </c>
-      <c r="E117" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G117" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P117" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="118" spans="1:19" ht="102" x14ac:dyDescent="0.2">
-      <c r="A118" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="B118" s="32" t="s">
-        <v>431</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="D118" s="25" t="s">
-        <v>28</v>
       </c>
       <c r="E118" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G118" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="153" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A119" s="25" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G119" s="25" t="b">
         <v>1</v>
@@ -7844,44 +7853,38 @@
         <v>93</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" ht="153" x14ac:dyDescent="0.2">
       <c r="A120" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="D120" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G120" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P120" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A121" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="B121" s="32" t="s">
+        <v>435</v>
+      </c>
+      <c r="C121" s="25" t="s">
         <v>436</v>
-      </c>
-      <c r="B120" s="32" t="s">
-        <v>437</v>
-      </c>
-      <c r="C120" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="D120" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E120" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G120" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P120" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R120" s="27" t="s">
-        <v>832</v>
-      </c>
-      <c r="S120" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A121" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="B121" s="32" t="s">
-        <v>440</v>
-      </c>
-      <c r="C121" s="25" t="s">
-        <v>441</v>
       </c>
       <c r="D121" s="25" t="s">
         <v>27</v>
@@ -7896,47 +7899,53 @@
         <v>93</v>
       </c>
       <c r="R121" s="27" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="S121" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="25" t="s">
+        <v>437</v>
+      </c>
+      <c r="B122" s="32" t="s">
+        <v>438</v>
+      </c>
+      <c r="C122" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="D122" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E122" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G122" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P122" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R122" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S122" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A123" s="25" t="s">
+        <v>440</v>
+      </c>
+      <c r="B123" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="C123" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="B122" s="32" t="s">
-        <v>443</v>
-      </c>
-      <c r="C122" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="D122" s="25" t="s">
+      <c r="D123" s="25" t="s">
         <v>30</v>
-      </c>
-      <c r="E122" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G122" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P122" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A123" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="B123" s="32" t="s">
-        <v>446</v>
-      </c>
-      <c r="C123" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="D123" s="25" t="s">
-        <v>27</v>
       </c>
       <c r="E123" s="25" t="s">
         <v>64</v>
@@ -7948,336 +7957,330 @@
         <v>97</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A124" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="B124" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="C124" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="D124" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E124" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G124" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P124" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A125" s="25" t="s">
+        <v>446</v>
+      </c>
+      <c r="B125" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="C125" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="B124" s="32" t="s">
+      <c r="D125" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E125" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G125" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P125" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R125" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S125" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A126" s="25" t="s">
         <v>449</v>
       </c>
-      <c r="C124" s="25" t="s">
+      <c r="B126" s="32" t="s">
         <v>450</v>
       </c>
-      <c r="D124" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E124" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G124" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P124" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R124" s="27" t="s">
-        <v>832</v>
-      </c>
-      <c r="S124" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A125" s="25" t="s">
+      <c r="C126" s="25" t="s">
         <v>451</v>
       </c>
-      <c r="B125" s="32" t="s">
+      <c r="D126" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G126" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P126" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="A127" s="25" t="s">
         <v>452</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="B127" s="32" t="s">
         <v>453</v>
       </c>
-      <c r="D125" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E125" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G125" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P125" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19" ht="102" x14ac:dyDescent="0.2">
-      <c r="A126" s="25" t="s">
+      <c r="C127" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="D127" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E127" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G127" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P127" s="27" t="s">
         <v>454</v>
       </c>
-      <c r="B126" s="32" t="s">
-        <v>455</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>457</v>
-      </c>
-      <c r="D126" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E126" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G126" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P126" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="R126" s="27" t="s">
-        <v>833</v>
-      </c>
-      <c r="S126" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A127" s="25" t="s">
-        <v>458</v>
-      </c>
-      <c r="B127" s="32" t="s">
-        <v>459</v>
-      </c>
-      <c r="C127" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="D127" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E127" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G127" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P127" s="27" t="s">
-        <v>93</v>
-      </c>
       <c r="R127" s="27" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="S127" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A128" s="25" t="s">
+        <v>456</v>
+      </c>
+      <c r="B128" s="32" t="s">
+        <v>457</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D128" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E128" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G128" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P128" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R128" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S128" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A129" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="B129" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="C129" s="25" t="s">
         <v>461</v>
       </c>
-      <c r="B128" s="32" t="s">
+      <c r="D129" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E129" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G129" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P129" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A130" s="25" t="s">
         <v>462</v>
       </c>
-      <c r="C128" s="25" t="s">
+      <c r="B130" s="32" t="s">
         <v>463</v>
       </c>
-      <c r="D128" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E128" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G128" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P128" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A129" s="25" t="s">
+      <c r="C130" s="25" t="s">
         <v>464</v>
       </c>
-      <c r="B129" s="32" t="s">
-        <v>465</v>
-      </c>
-      <c r="C129" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="D129" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E129" s="25" t="s">
+      <c r="D130" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E130" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G129" s="25" t="b">
+      <c r="G130" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P129" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R129" s="27" t="s">
-        <v>832</v>
-      </c>
-      <c r="S129" s="27" t="s">
+      <c r="P130" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R130" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S130" s="27" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="130" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A130" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="B130" s="32" t="s">
-        <v>468</v>
-      </c>
-      <c r="C130" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="D130" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E130" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G130" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P130" s="27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="131" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A131" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="B131" s="32" t="s">
+        <v>466</v>
+      </c>
+      <c r="C131" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="D131" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E131" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G131" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P131" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A132" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>469</v>
+      </c>
+      <c r="C132" s="25" t="s">
         <v>470</v>
       </c>
-      <c r="B131" s="32" t="s">
+      <c r="D132" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E132" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G132" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P132" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R132" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S132" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A133" s="25" t="s">
         <v>471</v>
       </c>
-      <c r="C131" s="25" t="s">
+      <c r="B133" s="32" t="s">
         <v>472</v>
       </c>
-      <c r="D131" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E131" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G131" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P131" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R131" s="27" t="s">
-        <v>832</v>
-      </c>
-      <c r="S131" s="27" t="s">
+      <c r="C133" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="D133" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E133" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G133" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P133" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="A134" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="B134" s="32" t="s">
+        <v>475</v>
+      </c>
+      <c r="C134" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="D134" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E134" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G134" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P134" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="R134" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="S134" s="27" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A132" s="25" t="s">
-        <v>473</v>
-      </c>
-      <c r="B132" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="C132" s="25" t="s">
-        <v>475</v>
-      </c>
-      <c r="D132" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E132" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G132" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P132" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="133" spans="1:19" ht="102" x14ac:dyDescent="0.2">
-      <c r="A133" s="25" t="s">
-        <v>476</v>
-      </c>
-      <c r="B133" s="32" t="s">
-        <v>477</v>
-      </c>
-      <c r="C133" s="25" t="s">
-        <v>478</v>
-      </c>
-      <c r="D133" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E133" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G133" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P133" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="R133" s="27" t="s">
-        <v>833</v>
-      </c>
-      <c r="S133" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="134" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A134" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="B134" s="32" t="s">
-        <v>480</v>
-      </c>
-      <c r="C134" s="25" t="s">
-        <v>481</v>
-      </c>
-      <c r="D134" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E134" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G134" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P134" s="27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="135" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A135" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="B135" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="C135" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="D135" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E135" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G135" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P135" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A136" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="B136" s="32" t="s">
+        <v>481</v>
+      </c>
+      <c r="C136" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="B135" s="32" t="s">
-        <v>483</v>
-      </c>
-      <c r="C135" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="D135" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E135" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G135" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P135" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R135" s="27" t="s">
-        <v>832</v>
-      </c>
-      <c r="S135" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="136" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A136" s="25" t="s">
-        <v>485</v>
-      </c>
-      <c r="B136" s="32" t="s">
-        <v>486</v>
-      </c>
-      <c r="C136" s="25" t="s">
-        <v>487</v>
-      </c>
       <c r="D136" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E136" s="25" t="s">
         <v>63</v>
@@ -8286,21 +8289,27 @@
         <v>1</v>
       </c>
       <c r="P136" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+      <c r="R136" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S136" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A137" s="25" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B137" s="32" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C137" s="25" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E137" s="25" t="s">
         <v>63</v>
@@ -8309,223 +8318,223 @@
         <v>1</v>
       </c>
       <c r="P137" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R137" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A138" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>487</v>
+      </c>
+      <c r="C138" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="D138" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E138" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G138" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P138" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R138" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="S138" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A139" s="25" t="s">
+        <v>489</v>
+      </c>
+      <c r="B139" s="32" t="s">
+        <v>490</v>
+      </c>
+      <c r="C139" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="D139" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E139" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G139" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P139" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="A140" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="B140" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>839</v>
+      </c>
+      <c r="D140" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E140" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G140" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P140" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="R140" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="S140" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A141" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="B141" s="32" t="s">
+        <v>495</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D141" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E141" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G141" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P141" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="R141" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A142" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="B142" s="32" t="s">
+        <v>498</v>
+      </c>
+      <c r="C142" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="D142" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E142" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G142" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P142" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A143" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="B143" s="32" t="s">
+        <v>501</v>
+      </c>
+      <c r="C143" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="D143" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E143" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G143" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P143" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R143" s="27" t="s">
         <v>832</v>
       </c>
-      <c r="S137" s="27" t="s">
+      <c r="S143" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A138" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="B138" s="32" t="s">
-        <v>492</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>493</v>
-      </c>
-      <c r="D138" s="25" t="s">
+    <row r="144" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A144" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>504</v>
+      </c>
+      <c r="C144" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="D144" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E138" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G138" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P138" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="139" spans="1:19" ht="102" x14ac:dyDescent="0.2">
-      <c r="A139" s="25" t="s">
-        <v>494</v>
-      </c>
-      <c r="B139" s="32" t="s">
-        <v>495</v>
-      </c>
-      <c r="C139" s="25" t="s">
-        <v>841</v>
-      </c>
-      <c r="D139" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E139" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G139" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P139" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="R139" s="27" t="s">
-        <v>833</v>
-      </c>
-      <c r="S139" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="140" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A140" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="B140" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="C140" s="25" t="s">
-        <v>498</v>
-      </c>
-      <c r="D140" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E140" s="25" t="s">
+      <c r="E144" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G140" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P140" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="R140" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="141" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A141" s="25" t="s">
-        <v>499</v>
-      </c>
-      <c r="B141" s="32" t="s">
-        <v>500</v>
-      </c>
-      <c r="C141" s="25" t="s">
-        <v>501</v>
-      </c>
-      <c r="D141" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E141" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G141" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P141" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="142" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A142" s="25" t="s">
-        <v>502</v>
-      </c>
-      <c r="B142" s="32" t="s">
-        <v>503</v>
-      </c>
-      <c r="C142" s="25" t="s">
-        <v>504</v>
-      </c>
-      <c r="D142" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E142" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G142" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P142" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R142" s="27" t="s">
-        <v>834</v>
-      </c>
-      <c r="S142" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="143" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A143" s="25" t="s">
-        <v>505</v>
-      </c>
-      <c r="B143" s="32" t="s">
+      <c r="G144" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P144" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+      <c r="A145" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="C143" s="25" t="s">
+      <c r="B145" s="32" t="s">
         <v>507</v>
       </c>
-      <c r="D143" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E143" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G143" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P143" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A144" s="25" t="s">
+      <c r="C145" s="25" t="s">
         <v>508</v>
-      </c>
-      <c r="B144" s="32" t="s">
-        <v>509</v>
-      </c>
-      <c r="C144" s="25" t="s">
-        <v>510</v>
-      </c>
-      <c r="D144" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E144" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G144" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P144" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" ht="68" x14ac:dyDescent="0.2">
-      <c r="A145" s="25" t="s">
-        <v>511</v>
-      </c>
-      <c r="B145" s="32" t="s">
-        <v>512</v>
-      </c>
-      <c r="C145" s="25" t="s">
-        <v>513</v>
       </c>
       <c r="D145" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="G145" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P145" s="27" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A146" s="25" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B146" s="32" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C146" s="25" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D146" s="25" t="s">
         <v>28</v>
@@ -8537,24 +8546,24 @@
         <v>0</v>
       </c>
       <c r="P146" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="147" spans="1:21" ht="187" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="25" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B147" s="32" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>835</v>
+        <v>514</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="G147" s="25" t="b">
         <v>0</v>
@@ -8562,25 +8571,16 @@
       <c r="P147" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R147" s="27" t="s">
-        <v>815</v>
-      </c>
-      <c r="S147" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="U147" s="27" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="148" spans="1:21" ht="170" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:21" ht="187" x14ac:dyDescent="0.2">
       <c r="A148" s="25" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D148" s="25" t="s">
         <v>27</v>
@@ -8595,24 +8595,24 @@
         <v>93</v>
       </c>
       <c r="R148" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S148" s="27" t="s">
         <v>68</v>
       </c>
       <c r="U148" s="27" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="149" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" ht="170" x14ac:dyDescent="0.2">
       <c r="A149" s="25" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B149" s="32" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C149" s="25" t="s">
-        <v>71</v>
+        <v>834</v>
       </c>
       <c r="D149" s="25" t="s">
         <v>27</v>
@@ -8627,21 +8627,24 @@
         <v>93</v>
       </c>
       <c r="R149" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S149" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="U149" s="27" t="s">
+        <v>835</v>
+      </c>
     </row>
     <row r="150" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A150" s="25" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B150" s="32" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C150" s="25" t="s">
-        <v>525</v>
+        <v>71</v>
       </c>
       <c r="D150" s="25" t="s">
         <v>27</v>
@@ -8656,7 +8659,7 @@
         <v>93</v>
       </c>
       <c r="R150" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S150" s="27" t="s">
         <v>68</v>
@@ -8664,13 +8667,13 @@
     </row>
     <row r="151" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A151" s="25" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B151" s="32" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C151" s="25" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D151" s="25" t="s">
         <v>27</v>
@@ -8685,7 +8688,7 @@
         <v>93</v>
       </c>
       <c r="R151" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S151" s="27" t="s">
         <v>68</v>
@@ -8693,13 +8696,13 @@
     </row>
     <row r="152" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A152" s="25" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>72</v>
+        <v>526</v>
       </c>
       <c r="D152" s="25" t="s">
         <v>27</v>
@@ -8714,21 +8717,21 @@
         <v>93</v>
       </c>
       <c r="R152" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S152" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A153" s="25" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B153" s="32" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D153" s="25" t="s">
         <v>27</v>
@@ -8743,21 +8746,21 @@
         <v>93</v>
       </c>
       <c r="R153" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S153" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A154" s="25" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B154" s="32" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C154" s="25" t="s">
-        <v>535</v>
+        <v>73</v>
       </c>
       <c r="D154" s="25" t="s">
         <v>27</v>
@@ -8772,7 +8775,7 @@
         <v>93</v>
       </c>
       <c r="R154" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S154" s="27" t="s">
         <v>68</v>
@@ -8780,13 +8783,13 @@
     </row>
     <row r="155" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A155" s="25" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B155" s="32" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>74</v>
+        <v>533</v>
       </c>
       <c r="D155" s="25" t="s">
         <v>27</v>
@@ -8801,7 +8804,7 @@
         <v>93</v>
       </c>
       <c r="R155" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S155" s="27" t="s">
         <v>68</v>
@@ -8809,13 +8812,13 @@
     </row>
     <row r="156" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A156" s="25" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B156" s="32" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D156" s="25" t="s">
         <v>27</v>
@@ -8830,7 +8833,7 @@
         <v>93</v>
       </c>
       <c r="R156" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S156" s="27" t="s">
         <v>68</v>
@@ -8838,13 +8841,13 @@
     </row>
     <row r="157" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A157" s="25" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B157" s="32" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D157" s="25" t="s">
         <v>27</v>
@@ -8859,7 +8862,7 @@
         <v>93</v>
       </c>
       <c r="R157" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S157" s="27" t="s">
         <v>68</v>
@@ -8867,13 +8870,13 @@
     </row>
     <row r="158" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A158" s="25" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B158" s="32" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D158" s="25" t="s">
         <v>27</v>
@@ -8888,21 +8891,21 @@
         <v>93</v>
       </c>
       <c r="R158" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="S158" s="27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A159" s="25" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B159" s="32" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>546</v>
+        <v>77</v>
       </c>
       <c r="D159" s="25" t="s">
         <v>27</v>
@@ -8911,13 +8914,13 @@
         <v>63</v>
       </c>
       <c r="G159" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P159" s="27" t="s">
         <v>93</v>
       </c>
       <c r="R159" s="27" t="s">
-        <v>88</v>
+        <v>813</v>
       </c>
       <c r="S159" s="27" t="s">
         <v>68</v>
@@ -8925,59 +8928,65 @@
     </row>
     <row r="160" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A160" s="25" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B160" s="32" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E160" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G160" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P160" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="161" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="R160" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="S160" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A161" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="B161" s="32" t="s">
+        <v>546</v>
+      </c>
+      <c r="C161" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="D161" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E161" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G161" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P161" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A162" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>549</v>
+      </c>
+      <c r="C162" s="25" t="s">
         <v>550</v>
-      </c>
-      <c r="B161" s="32" t="s">
-        <v>551</v>
-      </c>
-      <c r="C161" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="D161" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E161" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G161" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P161" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="162" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A162" s="25" t="s">
-        <v>553</v>
-      </c>
-      <c r="B162" s="32" t="s">
-        <v>554</v>
-      </c>
-      <c r="C162" s="25" t="s">
-        <v>555</v>
       </c>
       <c r="D162" s="25" t="s">
         <v>28</v>
@@ -8994,13 +9003,13 @@
     </row>
     <row r="163" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A163" s="25" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B163" s="32" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="D163" s="25" t="s">
         <v>28</v>
@@ -9017,16 +9026,16 @@
     </row>
     <row r="164" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A164" s="25" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B164" s="32" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D164" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E164" s="25" t="s">
         <v>64</v>
@@ -9038,15 +9047,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="165" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A165" s="25" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B165" s="32" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="D165" s="25" t="s">
         <v>27</v>
@@ -9061,15 +9070,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="166" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A166" s="25" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B166" s="32" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D166" s="25" t="s">
         <v>27</v>
@@ -9084,18 +9093,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="167" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A167" s="25" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B167" s="32" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D167" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E167" s="25" t="s">
         <v>64</v>
@@ -9107,15 +9116,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="168" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A168" s="25" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B168" s="32" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D168" s="25" t="s">
         <v>28</v>
@@ -9132,13 +9141,13 @@
     </row>
     <row r="169" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A169" s="25" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B169" s="32" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D169" s="25" t="s">
         <v>28</v>
@@ -9153,15 +9162,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="170" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A170" s="25" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B170" s="32" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D170" s="25" t="s">
         <v>28</v>
@@ -9176,15 +9185,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A171" s="25" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B171" s="32" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D171" s="25" t="s">
         <v>28</v>
@@ -9201,13 +9210,13 @@
     </row>
     <row r="172" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A172" s="25" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B172" s="32" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D172" s="25" t="s">
         <v>28</v>
@@ -9224,22 +9233,22 @@
     </row>
     <row r="173" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A173" s="25" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B173" s="32" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E173" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G173" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P173" s="27" t="s">
         <v>93</v>
@@ -9247,22 +9256,22 @@
     </row>
     <row r="174" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A174" s="25" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B174" s="32" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E174" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G174" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P174" s="27" t="s">
         <v>93</v>
@@ -9270,45 +9279,39 @@
     </row>
     <row r="175" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A175" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="B175" s="32" t="s">
+        <v>588</v>
+      </c>
+      <c r="C175" s="25" t="s">
+        <v>589</v>
+      </c>
+      <c r="D175" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E175" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G175" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P175" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A176" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="B176" s="32" t="s">
+        <v>591</v>
+      </c>
+      <c r="C176" s="25" t="s">
         <v>592</v>
       </c>
-      <c r="B175" s="32" t="s">
-        <v>593</v>
-      </c>
-      <c r="C175" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="D175" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E175" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G175" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P175" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R175" s="27" t="s">
-        <v>819</v>
-      </c>
-      <c r="S175" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="176" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A176" s="25" t="s">
-        <v>595</v>
-      </c>
-      <c r="B176" s="32" t="s">
-        <v>596</v>
-      </c>
-      <c r="C176" s="25" t="s">
-        <v>597</v>
-      </c>
       <c r="D176" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E176" s="25" t="s">
         <v>137</v>
@@ -9319,65 +9322,71 @@
       <c r="P176" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+      <c r="R176" s="27" t="s">
+        <v>817</v>
+      </c>
+      <c r="S176" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="177" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A177" s="25" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B177" s="32" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C177" s="25" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D177" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E177" s="25" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="G177" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P177" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="178" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A178" s="25" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B178" s="32" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D178" s="25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E178" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G178" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P178" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="179" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A179" s="25" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B179" s="32" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E179" s="25" t="s">
         <v>64</v>
@@ -9389,15 +9398,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="180" spans="1:22" ht="17" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A180" s="25" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B180" s="32" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D180" s="25" t="s">
         <v>27</v>
@@ -9412,38 +9421,38 @@
         <v>93</v>
       </c>
     </row>
-    <row r="181" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A181" s="25" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B181" s="32" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D181" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E181" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G181" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P181" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="182" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A182" s="25" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B182" s="32" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D182" s="25" t="s">
         <v>28</v>
@@ -9458,41 +9467,41 @@
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A183" s="25" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B183" s="32" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E183" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G183" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P183" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="184" spans="1:22" ht="102" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A184" s="25" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B184" s="32" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D184" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E184" s="25" t="s">
         <v>64</v>
@@ -9504,18 +9513,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="185" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A185" s="25" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B185" s="32" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C185" s="25" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="D185" s="25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E185" s="25" t="s">
         <v>64</v>
@@ -9527,18 +9536,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="186" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A186" s="25" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B186" s="32" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D186" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E186" s="25" t="s">
         <v>64</v>
@@ -9550,18 +9559,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="187" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A187" s="25" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B187" s="32" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D187" s="25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E187" s="25" t="s">
         <v>64</v>
@@ -9573,18 +9582,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="188" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B188" s="32" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E188" s="25" t="s">
         <v>64</v>
@@ -9595,40 +9604,40 @@
       <c r="P188" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="V188" s="31"/>
-    </row>
-    <row r="189" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B189" s="32" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E189" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G189" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P189" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+      <c r="V189" s="31"/>
+    </row>
+    <row r="190" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B190" s="32" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="D190" s="25" t="s">
         <v>27</v>
@@ -9643,15 +9652,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="191" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B191" s="32" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D191" s="25" t="s">
         <v>27</v>
@@ -9660,53 +9669,50 @@
         <v>64</v>
       </c>
       <c r="G191" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P191" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="192" spans="1:22" ht="136" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
+        <v>638</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>639</v>
+      </c>
+      <c r="C192" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="D192" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E192" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G192" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P192" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" ht="136" x14ac:dyDescent="0.2">
+      <c r="A193" s="25" t="s">
+        <v>641</v>
+      </c>
+      <c r="B193" s="32" t="s">
+        <v>642</v>
+      </c>
+      <c r="C193" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="B192" s="32" t="s">
-        <v>644</v>
-      </c>
-      <c r="C192" s="25" t="s">
-        <v>645</v>
-      </c>
-      <c r="D192" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E192" s="25" t="s">
+      <c r="D193" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E193" s="25" t="s">
         <v>63</v>
-      </c>
-      <c r="G192" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P192" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R192" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="193" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A193" s="25" t="s">
-        <v>646</v>
-      </c>
-      <c r="B193" s="32" t="s">
-        <v>647</v>
-      </c>
-      <c r="C193" s="25" t="s">
-        <v>648</v>
-      </c>
-      <c r="D193" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E193" s="25" t="s">
-        <v>64</v>
       </c>
       <c r="G193" s="25" t="b">
         <v>1</v>
@@ -9714,19 +9720,22 @@
       <c r="P193" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="194" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="R193" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="B194" s="32" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D194" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E194" s="25" t="s">
         <v>64</v>
@@ -9740,62 +9749,62 @@
     </row>
     <row r="195" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B195" s="32" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D195" s="25" t="s">
         <v>26</v>
       </c>
       <c r="E195" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G195" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P195" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A196" s="25" t="s">
+        <v>650</v>
+      </c>
+      <c r="B196" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="C196" s="25" t="s">
+        <v>652</v>
+      </c>
+      <c r="D196" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E196" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G195" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P195" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="196" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A196" s="25" t="s">
+      <c r="G196" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P196" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A197" s="25" t="s">
+        <v>653</v>
+      </c>
+      <c r="B197" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="C197" s="25" t="s">
         <v>655</v>
       </c>
-      <c r="B196" s="32" t="s">
-        <v>656</v>
-      </c>
-      <c r="C196" s="25" t="s">
-        <v>657</v>
-      </c>
-      <c r="D196" s="25" t="s">
+      <c r="D197" s="25" t="s">
         <v>30</v>
-      </c>
-      <c r="E196" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G196" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P196" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="197" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A197" s="25" t="s">
-        <v>658</v>
-      </c>
-      <c r="B197" s="32" t="s">
-        <v>659</v>
-      </c>
-      <c r="C197" s="25" t="s">
-        <v>660</v>
-      </c>
-      <c r="D197" s="25" t="s">
-        <v>28</v>
       </c>
       <c r="E197" s="25" t="s">
         <v>64</v>
@@ -9804,44 +9813,44 @@
         <v>0</v>
       </c>
       <c r="P197" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="198" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A198" s="25" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B198" s="32" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E198" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G198" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P198" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="199" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A199" s="25" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B199" s="32" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E199" s="25" t="s">
         <v>64</v>
@@ -9853,15 +9862,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="200" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A200" s="25" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B200" s="32" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="D200" s="25" t="s">
         <v>28</v>
@@ -9870,116 +9879,116 @@
         <v>64</v>
       </c>
       <c r="G200" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P200" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A201" s="25" t="s">
+        <v>665</v>
+      </c>
+      <c r="B201" s="32" t="s">
+        <v>666</v>
+      </c>
+      <c r="C201" s="25" t="s">
+        <v>667</v>
+      </c>
+      <c r="D201" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E201" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G201" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P201" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="201" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A201" s="25" t="s">
+    <row r="202" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A202" s="25" t="s">
+        <v>668</v>
+      </c>
+      <c r="B202" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="C202" s="25" t="s">
         <v>670</v>
       </c>
-      <c r="B201" s="32" t="s">
-        <v>671</v>
-      </c>
-      <c r="C201" s="25" t="s">
-        <v>672</v>
-      </c>
-      <c r="D201" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E201" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G201" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P201" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="R201" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="202" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A202" s="25" t="s">
-        <v>673</v>
-      </c>
-      <c r="B202" s="32" t="s">
-        <v>674</v>
-      </c>
-      <c r="C202" s="25" t="s">
-        <v>675</v>
-      </c>
       <c r="D202" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E202" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G202" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P202" s="27" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="203" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="R202" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A203" s="25" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B203" s="32" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="D203" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E203" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G203" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P203" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="204" spans="1:19" ht="170" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A204" s="25" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B204" s="32" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E204" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G204" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P204" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="205" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:19" ht="170" x14ac:dyDescent="0.2">
       <c r="A205" s="25" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B205" s="32" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="D205" s="25" t="s">
         <v>27</v>
@@ -9994,15 +10003,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="206" spans="1:19" ht="170" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A206" s="25" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B206" s="32" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D206" s="25" t="s">
         <v>27</v>
@@ -10017,125 +10026,119 @@
         <v>93</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:19" ht="170" x14ac:dyDescent="0.2">
       <c r="A207" s="25" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B207" s="32" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D207" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E207" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G207" s="25" t="b">
         <v>1</v>
       </c>
       <c r="P207" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A208" s="25" t="s">
+        <v>686</v>
+      </c>
+      <c r="B208" s="32" t="s">
+        <v>687</v>
+      </c>
+      <c r="C208" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="D208" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E208" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G208" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P208" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="R208" s="27" t="s">
+        <v>805</v>
+      </c>
+      <c r="S208" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A209" s="25" t="s">
         <v>690</v>
       </c>
-      <c r="R207" s="27" t="s">
-        <v>807</v>
-      </c>
-      <c r="S207" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="208" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A208" s="25" t="s">
+      <c r="B209" s="32" t="s">
+        <v>691</v>
+      </c>
+      <c r="C209" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D209" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E209" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G209" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P209" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A210" s="25" t="s">
         <v>692</v>
       </c>
-      <c r="B208" s="32" t="s">
+      <c r="B210" s="32" t="s">
         <v>693</v>
       </c>
-      <c r="C208" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D208" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E208" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G208" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P208" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="209" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A209" s="25" t="s">
+      <c r="C210" s="25" t="s">
+        <v>695</v>
+      </c>
+      <c r="D210" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E210" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G210" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P210" s="27" t="s">
         <v>694</v>
       </c>
-      <c r="B209" s="32" t="s">
-        <v>695</v>
-      </c>
-      <c r="C209" s="25" t="s">
+      <c r="R210" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A211" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="B211" s="32" t="s">
         <v>697</v>
       </c>
-      <c r="D209" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E209" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G209" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P209" s="27" t="s">
-        <v>696</v>
-      </c>
-      <c r="R209" s="27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="210" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A210" s="25" t="s">
+      <c r="C211" s="25" t="s">
         <v>698</v>
       </c>
-      <c r="B210" s="32" t="s">
-        <v>699</v>
-      </c>
-      <c r="C210" s="25" t="s">
-        <v>700</v>
-      </c>
-      <c r="D210" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E210" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G210" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P210" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="R210" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="S210" s="27" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="211" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A211" s="25" t="s">
-        <v>701</v>
-      </c>
-      <c r="B211" s="32" t="s">
-        <v>702</v>
-      </c>
-      <c r="C211" s="25" t="s">
-        <v>703</v>
-      </c>
       <c r="D211" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E211" s="25" t="s">
         <v>63</v>
@@ -10144,44 +10147,50 @@
         <v>0</v>
       </c>
       <c r="P211" s="27" t="s">
-        <v>93</v>
+        <v>189</v>
+      </c>
+      <c r="R211" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="S211" s="27" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="212" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A212" s="25" t="s">
+        <v>699</v>
+      </c>
+      <c r="B212" s="32" t="s">
+        <v>700</v>
+      </c>
+      <c r="C212" s="25" t="s">
+        <v>701</v>
+      </c>
+      <c r="D212" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E212" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G212" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P212" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A213" s="25" t="s">
+        <v>702</v>
+      </c>
+      <c r="B213" s="32" t="s">
+        <v>703</v>
+      </c>
+      <c r="C213" s="25" t="s">
         <v>704</v>
       </c>
-      <c r="B212" s="32" t="s">
-        <v>705</v>
-      </c>
-      <c r="C212" s="25" t="s">
-        <v>706</v>
-      </c>
-      <c r="D212" s="25" t="s">
+      <c r="D213" s="25" t="s">
         <v>28</v>
-      </c>
-      <c r="E212" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G212" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P212" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="213" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A213" s="25" t="s">
-        <v>707</v>
-      </c>
-      <c r="B213" s="32" t="s">
-        <v>708</v>
-      </c>
-      <c r="C213" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="D213" s="25" t="s">
-        <v>27</v>
       </c>
       <c r="E213" s="25" t="s">
         <v>64</v>
@@ -10193,18 +10202,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="214" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A214" s="25" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B214" s="32" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C214" s="25" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="D214" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E214" s="25" t="s">
         <v>64</v>
@@ -10216,15 +10225,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="215" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A215" s="25" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B215" s="32" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C215" s="25" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D215" s="25" t="s">
         <v>28</v>
@@ -10241,16 +10250,16 @@
     </row>
     <row r="216" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A216" s="25" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="B216" s="32" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C216" s="25" t="s">
-        <v>79</v>
+        <v>713</v>
       </c>
       <c r="D216" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E216" s="25" t="s">
         <v>64</v>
@@ -10262,15 +10271,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="217" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A217" s="25" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B217" s="32" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C217" s="25" t="s">
-        <v>720</v>
+        <v>79</v>
       </c>
       <c r="D217" s="25" t="s">
         <v>27</v>
@@ -10285,15 +10294,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="218" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A218" s="25" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B218" s="32" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C218" s="25" t="s">
-        <v>80</v>
+        <v>718</v>
       </c>
       <c r="D218" s="25" t="s">
         <v>27</v>
@@ -10308,15 +10317,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="219" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A219" s="25" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B219" s="32" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C219" s="25" t="s">
-        <v>725</v>
+        <v>80</v>
       </c>
       <c r="D219" s="25" t="s">
         <v>27</v>
@@ -10331,18 +10340,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="220" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A220" s="25" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B220" s="32" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C220" s="25" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="D220" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E220" s="25" t="s">
         <v>64</v>
@@ -10354,18 +10363,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="221" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A221" s="25" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B221" s="32" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C221" s="25" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="D221" s="25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E221" s="25" t="s">
         <v>64</v>
@@ -10379,65 +10388,65 @@
     </row>
     <row r="222" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A222" s="25" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B222" s="32" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C222" s="25" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E222" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G222" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P222" s="27" t="s">
         <v>93</v>
-      </c>
-      <c r="R222" s="27" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="223" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A223" s="25" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B223" s="32" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C223" s="25" t="s">
+        <v>732</v>
+      </c>
+      <c r="D223" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E223" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G223" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P223" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R223" s="27" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A224" s="25" t="s">
+        <v>733</v>
+      </c>
+      <c r="B224" s="32" t="s">
+        <v>734</v>
+      </c>
+      <c r="C224" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D223" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E223" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G223" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P223" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="224" spans="1:19" ht="136" x14ac:dyDescent="0.2">
-      <c r="A224" s="25" t="s">
-        <v>737</v>
-      </c>
-      <c r="B224" s="32" t="s">
-        <v>738</v>
-      </c>
-      <c r="C224" s="25" t="s">
-        <v>739</v>
-      </c>
       <c r="D224" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E224" s="25" t="s">
         <v>64</v>
@@ -10449,64 +10458,64 @@
         <v>93</v>
       </c>
     </row>
-    <row r="225" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A225" s="25" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="B225" s="32" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C225" s="25" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D225" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E225" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G225" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P225" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A226" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="B226" s="32" t="s">
+        <v>739</v>
+      </c>
+      <c r="C226" s="25" t="s">
+        <v>740</v>
+      </c>
+      <c r="D226" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E226" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G225" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P225" s="27" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="226" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A226" s="25" t="s">
+      <c r="G226" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P226" s="27" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A227" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="B227" s="32" t="s">
+        <v>742</v>
+      </c>
+      <c r="C227" s="25" t="s">
         <v>743</v>
       </c>
-      <c r="B226" s="32" t="s">
-        <v>744</v>
-      </c>
-      <c r="C226" s="25" t="s">
-        <v>745</v>
-      </c>
-      <c r="D226" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E226" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G226" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P226" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="227" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A227" s="25" t="s">
-        <v>746</v>
-      </c>
-      <c r="B227" s="32" t="s">
-        <v>747</v>
-      </c>
-      <c r="C227" s="25" t="s">
-        <v>748</v>
-      </c>
       <c r="D227" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E227" s="25" t="s">
         <v>64</v>
@@ -10520,117 +10529,117 @@
     </row>
     <row r="228" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A228" s="25" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B228" s="32" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C228" s="25" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="D228" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E228" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G228" s="25" t="b">
         <v>0</v>
       </c>
       <c r="P228" s="27" t="s">
         <v>93</v>
-      </c>
-      <c r="R228" s="27" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="229" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A229" s="25" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B229" s="32" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C229" s="25" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E229" s="25" t="s">
         <v>63</v>
       </c>
       <c r="G229" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P229" s="27" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="R229" s="27" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="230" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A230" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="B230" s="32" t="s">
+        <v>751</v>
+      </c>
+      <c r="C230" s="25" t="s">
+        <v>752</v>
+      </c>
+      <c r="D230" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E230" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G230" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P230" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A231" s="25" t="s">
+        <v>753</v>
+      </c>
+      <c r="B231" s="32" t="s">
+        <v>754</v>
+      </c>
+      <c r="C231" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="B230" s="32" t="s">
-        <v>756</v>
-      </c>
-      <c r="C230" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="D230" s="25" t="s">
+      <c r="D231" s="25" t="s">
         <v>30</v>
-      </c>
-      <c r="E230" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G230" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P230" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="231" spans="1:19" ht="119" x14ac:dyDescent="0.2">
-      <c r="A231" s="25" t="s">
-        <v>758</v>
-      </c>
-      <c r="B231" s="32" t="s">
-        <v>759</v>
-      </c>
-      <c r="C231" s="25" t="s">
-        <v>760</v>
-      </c>
-      <c r="D231" s="25" t="s">
-        <v>29</v>
       </c>
       <c r="E231" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G231" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P231" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="232" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:19" ht="119" x14ac:dyDescent="0.2">
       <c r="A232" s="25" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="B232" s="32" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C232" s="25" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="D232" s="25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E232" s="25" t="s">
         <v>64</v>
       </c>
       <c r="G232" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P232" s="27" t="s">
         <v>93</v>
@@ -10638,13 +10647,13 @@
     </row>
     <row r="233" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A233" s="25" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B233" s="32" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C233" s="25" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="D233" s="25" t="s">
         <v>27</v>
@@ -10659,21 +10668,21 @@
         <v>93</v>
       </c>
     </row>
-    <row r="234" spans="1:19" ht="204" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A234" s="25" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="B234" s="32" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C234" s="25" t="s">
-        <v>842</v>
+        <v>764</v>
       </c>
       <c r="D234" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E234" s="25" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="G234" s="25" t="b">
         <v>0</v>
@@ -10681,19 +10690,16 @@
       <c r="P234" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="R234" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="235" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="235" spans="1:19" ht="204" x14ac:dyDescent="0.2">
       <c r="A235" s="25" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B235" s="32" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C235" s="25" t="s">
-        <v>771</v>
+        <v>840</v>
       </c>
       <c r="D235" s="25" t="s">
         <v>27</v>
@@ -10708,24 +10714,21 @@
         <v>93</v>
       </c>
       <c r="R235" s="27" t="s">
-        <v>806</v>
-      </c>
-      <c r="S235" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="236" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A236" s="25" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B236" s="32" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C236" s="25" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D236" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E236" s="25" t="s">
         <v>137</v>
@@ -10736,68 +10739,74 @@
       <c r="P236" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="237" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="R236" s="27" t="s">
+        <v>804</v>
+      </c>
+      <c r="S236" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A237" s="25" t="s">
+        <v>770</v>
+      </c>
+      <c r="B237" s="32" t="s">
+        <v>771</v>
+      </c>
+      <c r="C237" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="D237" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E237" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G237" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P237" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="A238" s="25" t="s">
+        <v>773</v>
+      </c>
+      <c r="B238" s="32" t="s">
+        <v>774</v>
+      </c>
+      <c r="C238" s="25" t="s">
         <v>775</v>
       </c>
-      <c r="B237" s="32" t="s">
+      <c r="D238" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E238" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G238" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P238" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="R238" s="27" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A239" s="25" t="s">
         <v>776</v>
       </c>
-      <c r="C237" s="25" t="s">
+      <c r="B239" s="32" t="s">
         <v>777</v>
       </c>
-      <c r="D237" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E237" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G237" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P237" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R237" s="27" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="238" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A238" s="25" t="s">
+      <c r="C239" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="B238" s="32" t="s">
-        <v>779</v>
-      </c>
-      <c r="C238" s="25" t="s">
-        <v>780</v>
-      </c>
-      <c r="D238" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E238" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G238" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P238" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="239" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A239" s="25" t="s">
-        <v>781</v>
-      </c>
-      <c r="B239" s="32" t="s">
-        <v>782</v>
-      </c>
-      <c r="C239" s="25" t="s">
-        <v>783</v>
-      </c>
       <c r="D239" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E239" s="25" t="s">
         <v>64</v>
@@ -10806,70 +10815,70 @@
         <v>0</v>
       </c>
       <c r="P239" s="27" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="240" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A240" s="25" t="s">
+        <v>779</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>780</v>
+      </c>
+      <c r="C240" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="D240" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E240" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G240" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P240" s="27" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" ht="68" x14ac:dyDescent="0.2">
+      <c r="A241" s="25" t="s">
+        <v>782</v>
+      </c>
+      <c r="B241" s="32" t="s">
+        <v>783</v>
+      </c>
+      <c r="C241" s="25" t="s">
         <v>784</v>
       </c>
-      <c r="B240" s="32" t="s">
+      <c r="D241" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E241" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G241" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P241" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="R241" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" ht="34" x14ac:dyDescent="0.2">
+      <c r="A242" s="25" t="s">
         <v>785</v>
       </c>
-      <c r="C240" s="25" t="s">
+      <c r="B242" s="32" t="s">
         <v>786</v>
       </c>
-      <c r="D240" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E240" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G240" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P240" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="R240" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" ht="34" x14ac:dyDescent="0.2">
-      <c r="A241" s="25" t="s">
+      <c r="C242" s="25" t="s">
         <v>787</v>
       </c>
-      <c r="B241" s="32" t="s">
-        <v>788</v>
-      </c>
-      <c r="C241" s="25" t="s">
-        <v>789</v>
-      </c>
-      <c r="D241" s="25" t="s">
+      <c r="D242" s="25" t="s">
         <v>28</v>
-      </c>
-      <c r="E241" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G241" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P241" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" ht="68" x14ac:dyDescent="0.2">
-      <c r="A242" s="25" t="s">
-        <v>790</v>
-      </c>
-      <c r="B242" s="32" t="s">
-        <v>791</v>
-      </c>
-      <c r="C242" s="25" t="s">
-        <v>792</v>
-      </c>
-      <c r="D242" s="25" t="s">
-        <v>29</v>
       </c>
       <c r="E242" s="25" t="s">
         <v>66</v>
@@ -10878,49 +10887,69 @@
         <v>0</v>
       </c>
       <c r="P242" s="27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" ht="68" x14ac:dyDescent="0.2">
+      <c r="A243" s="25" t="s">
+        <v>788</v>
+      </c>
+      <c r="B243" s="32" t="s">
+        <v>789</v>
+      </c>
+      <c r="C243" s="25" t="s">
+        <v>790</v>
+      </c>
+      <c r="D243" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E243" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G243" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P243" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B243" s="32"/>
-    </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B244" s="32"/>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B245" s="32"/>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B246" s="32"/>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B247" s="32"/>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B248" s="32"/>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B249" s="32"/>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B250" s="32"/>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B251" s="32"/>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B252" s="32"/>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B253" s="32"/>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B254" s="32"/>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B255" s="32"/>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B256" s="32"/>
     </row>
     <row r="257" spans="2:2" x14ac:dyDescent="0.2">
@@ -11133,15 +11162,8 @@
     <row r="326" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B326" s="32"/>
     </row>
-    <row r="327" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="M327" s="30" t="str" cm="1">
-        <f t="array" ref="M327">PAGE_NAME(B327)</f>
-        <v/>
-      </c>
-      <c r="N327" s="30" t="str" cm="1">
-        <f t="array" ref="N327">SECTION_NAME(B327)</f>
-        <v/>
-      </c>
+    <row r="327" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B327" s="32"/>
     </row>
     <row r="328" spans="2:14" ht="17" x14ac:dyDescent="0.2">
       <c r="M328" s="30" t="str" cm="1">
@@ -11334,7 +11356,6 @@
       </c>
     </row>
     <row r="347" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B347" s="32"/>
       <c r="M347" s="30" t="str" cm="1">
         <f t="array" ref="M347">PAGE_NAME(B347)</f>
         <v/>
@@ -11345,6 +11366,7 @@
       </c>
     </row>
     <row r="348" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="B348" s="32"/>
       <c r="M348" s="30" t="str" cm="1">
         <f t="array" ref="M348">PAGE_NAME(B348)</f>
         <v/>
@@ -12224,16 +12246,26 @@
         <v/>
       </c>
     </row>
+    <row r="436" spans="13:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="M436" s="30" t="str" cm="1">
+        <f t="array" ref="M436">PAGE_NAME(B436)</f>
+        <v/>
+      </c>
+      <c r="N436" s="30" t="str" cm="1">
+        <f t="array" ref="N436">SECTION_NAME(B436)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U435" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
+  <autoFilter ref="A1:U436" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B24" r:id="rId1" location="ci-c-dev-3" xr:uid="{09A37A58-2BBF-FA48-99E7-8234535ED081}"/>
-    <hyperlink ref="B93" r:id="rId2" location="ci-c-found-36" xr:uid="{E9061C6B-069C-4F41-865D-1DCDB9B7CD5D}"/>
-    <hyperlink ref="B60" r:id="rId3" location="ci-c-found-6" xr:uid="{33B79C46-F26D-3345-9F9E-821047C0E3E2}"/>
+    <hyperlink ref="B94" r:id="rId2" location="ci-c-found-36" xr:uid="{E9061C6B-069C-4F41-865D-1DCDB9B7CD5D}"/>
+    <hyperlink ref="B61" r:id="rId3" location="ci-c-found-6" xr:uid="{33B79C46-F26D-3345-9F9E-821047C0E3E2}"/>
     <hyperlink ref="B10" r:id="rId4" location="ci-c-conf-5" xr:uid="{F659C0EC-431B-F840-B805-94301197C0AF}"/>
     <hyperlink ref="B15" r:id="rId5" location="ci-c-conf-10" xr:uid="{F087E38F-0649-264B-B4E3-ABE51917A024}"/>
-    <hyperlink ref="B234" r:id="rId6" location="ci-c-sec-1" xr:uid="{AB92F42F-5550-4A44-B1E0-DE9778C6CC21}"/>
+    <hyperlink ref="B235" r:id="rId6" location="ci-c-sec-1" xr:uid="{AB92F42F-5550-4A44-B1E0-DE9778C6CC21}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -12243,19 +12275,19 @@
           <x14:formula1>
             <xm:f>'Column Data'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G300:G1048576 G2:G298</xm:sqref>
+          <xm:sqref>G301:G1048576 G2:G299</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4866B9BF-5615-6646-965F-909D4D65F2A5}">
           <x14:formula1>
             <xm:f>'Column Data'!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D300:D1048576 D2:D298</xm:sqref>
+          <xm:sqref>D301:D1048576 D2:D299</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4FB27A2-804E-CB49-B85C-BBEE0C688B4F}">
           <x14:formula1>
             <xm:f>'Column Data'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K300:K1048576 I300:I1048576 K2:K298 I2:I298</xm:sqref>
+          <xm:sqref>K301:K1048576 I301:I1048576 I2:I299 K2:K299</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12287,7 +12319,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -12349,15 +12381,15 @@
         <v>45</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="153" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -12495,6 +12527,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -12748,29 +12802,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45EEC221-F5CD-4DEF-B390-EE14E23A8785}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12788,30 +12846,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/lib/davinci_crd_test_kit/requirements/hl7.fhir.us.davinci-crd_2.2.1_requirements.xlsx
+++ b/lib/davinci_crd_test_kit/requirements/hl7.fhir.us.davinci-crd_2.2.1_requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-crd-test-kit/lib/davinci_crd_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7AD7FE-7657-FE43-8930-18452B3BCEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D8BDCC-D990-3A4A-BC81-4F6CB6560460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="760" windowWidth="34240" windowHeight="21260" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2367,9 +2367,6 @@
     <t>https://hl7.org/fhir/us/davinci-crd/2.2.1/en/foundation.html#ci-c-found-25</t>
   </si>
   <si>
-    <t>Clients **SHALL** be able to supply the information listed in the bullets above via prefetch for the request resources they support when data exists using the search parameters and FHIRPath expressions covered in the [standard prefetch](https://hl7.org/fhir/us/davinci-crd/2.2.1/en/conformancedetails.html#standard-prefetch) section below. This includes the ability to fetch subsets of the specified queries.</t>
-  </si>
-  <si>
     <t>found-26</t>
   </si>
   <si>
@@ -3929,6 +3926,9 @@
   </si>
   <si>
     <t>CRD clients **SHALL** only invoke hooks on payer services where ... there is no recorded indication the patient intends to bypass insurance coverage (i.e. the service or product is not flagged as 'patient-pay').</t>
+  </si>
+  <si>
+    <t>Clients **SHALL** be able to supply the information listed in the bullets above via prefetch for the request resources they support when data exists using the search parameters and FHIRPath expressions covered in the [standard prefetch](https://hl7.org/fhir/us/davinci-crd/2.2.1/en/foundation.html#standard-prefetch) section below. This includes the ability to fetch subsets of the specified queries.</t>
   </si>
 </sst>
 </file>
@@ -4924,7 +4924,7 @@
         <v>23</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="T1" s="39" t="s">
         <v>24</v>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="Q2" s="27"/>
       <c r="R2" s="27" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="S2" s="27" t="s">
         <v>68</v>
@@ -5083,7 +5083,7 @@
         <v>93</v>
       </c>
       <c r="R6" s="27" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="S6" s="27" t="s">
         <v>68</v>
@@ -5135,10 +5135,10 @@
         <v>93</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="S8" s="27" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -5213,7 +5213,7 @@
         <v>82</v>
       </c>
       <c r="S11" s="27" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="119" x14ac:dyDescent="0.2">
@@ -5311,7 +5311,7 @@
         <v>84</v>
       </c>
       <c r="S15" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="16" spans="1:32" ht="68" x14ac:dyDescent="0.2">
@@ -5386,10 +5386,10 @@
         <v>93</v>
       </c>
       <c r="R18" s="27" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="S18" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="68" x14ac:dyDescent="0.2">
@@ -5956,7 +5956,7 @@
         <v>97</v>
       </c>
       <c r="R42" s="27" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="85" x14ac:dyDescent="0.2">
@@ -5982,7 +5982,7 @@
         <v>97</v>
       </c>
       <c r="R43" s="27" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="51" x14ac:dyDescent="0.2">
@@ -6008,7 +6008,7 @@
         <v>97</v>
       </c>
       <c r="R44" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="85" x14ac:dyDescent="0.2">
@@ -6059,13 +6059,13 @@
     </row>
     <row r="47" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A47" s="25" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B47" s="32" t="s">
         <v>230</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D47" s="25" t="s">
         <v>27</v>
@@ -6085,13 +6085,13 @@
     </row>
     <row r="48" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A48" s="25" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>230</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D48" s="25" t="s">
         <v>27</v>
@@ -6423,7 +6423,7 @@
         <v>189</v>
       </c>
       <c r="R61" s="27" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="S61" s="27" t="s">
         <v>68</v>
@@ -6751,7 +6751,7 @@
         <v>93</v>
       </c>
       <c r="R75" s="27" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="S75" s="27" t="s">
         <v>68</v>
@@ -6780,7 +6780,7 @@
         <v>97</v>
       </c>
       <c r="R76" s="27" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="S76" s="27" t="s">
         <v>68</v>
@@ -6832,7 +6832,7 @@
         <v>97</v>
       </c>
       <c r="R78" s="27" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="S78" s="27" t="s">
         <v>68</v>
@@ -6861,7 +6861,7 @@
         <v>93</v>
       </c>
       <c r="R79" s="27" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="S79" s="27" t="s">
         <v>68</v>
@@ -6869,13 +6869,13 @@
     </row>
     <row r="80" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A80" s="25" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B80" s="32" t="s">
         <v>324</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>325</v>
+        <v>844</v>
       </c>
       <c r="D80" s="25" t="s">
         <v>27</v>
@@ -6890,7 +6890,7 @@
         <v>93</v>
       </c>
       <c r="R80" s="27" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="S80" s="27" t="s">
         <v>68</v>
@@ -6898,13 +6898,13 @@
     </row>
     <row r="81" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A81" s="25" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B81" s="32" t="s">
         <v>324</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D81" s="25" t="s">
         <v>27</v>
@@ -6919,7 +6919,7 @@
         <v>93</v>
       </c>
       <c r="R81" s="27" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="S81" s="27" t="s">
         <v>68</v>
@@ -6927,13 +6927,13 @@
     </row>
     <row r="82" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="B82" s="32" t="s">
+      <c r="C82" s="25" t="s">
         <v>327</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>328</v>
       </c>
       <c r="D82" s="25" t="s">
         <v>26</v>
@@ -6950,13 +6950,13 @@
     </row>
     <row r="83" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B83" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="B83" s="32" t="s">
+      <c r="C83" s="25" t="s">
         <v>330</v>
-      </c>
-      <c r="C83" s="25" t="s">
-        <v>331</v>
       </c>
       <c r="D83" s="25" t="s">
         <v>28</v>
@@ -6973,13 +6973,13 @@
     </row>
     <row r="84" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="B84" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="B84" s="32" t="s">
+      <c r="C84" s="25" t="s">
         <v>333</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>334</v>
       </c>
       <c r="D84" s="25" t="s">
         <v>28</v>
@@ -6996,13 +6996,13 @@
     </row>
     <row r="85" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B85" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="C85" s="25" t="s">
         <v>336</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>337</v>
       </c>
       <c r="D85" s="25" t="s">
         <v>27</v>
@@ -7019,13 +7019,13 @@
     </row>
     <row r="86" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B86" s="32" t="s">
         <v>338</v>
       </c>
-      <c r="B86" s="32" t="s">
+      <c r="C86" s="25" t="s">
         <v>339</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>340</v>
       </c>
       <c r="D86" s="25" t="s">
         <v>29</v>
@@ -7042,13 +7042,13 @@
     </row>
     <row r="87" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A87" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="B87" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="B87" s="32" t="s">
+      <c r="C87" s="25" t="s">
         <v>342</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>343</v>
       </c>
       <c r="D87" s="25" t="s">
         <v>27</v>
@@ -7063,7 +7063,7 @@
         <v>97</v>
       </c>
       <c r="R87" s="27" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="S87" s="27" t="s">
         <v>68</v>
@@ -7071,13 +7071,13 @@
     </row>
     <row r="88" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A88" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="B88" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="B88" s="32" t="s">
+      <c r="C88" s="25" t="s">
         <v>345</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>346</v>
       </c>
       <c r="D88" s="25" t="s">
         <v>30</v>
@@ -7094,13 +7094,13 @@
     </row>
     <row r="89" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="B89" s="32" t="s">
         <v>347</v>
       </c>
-      <c r="B89" s="32" t="s">
+      <c r="C89" s="25" t="s">
         <v>348</v>
-      </c>
-      <c r="C89" s="25" t="s">
-        <v>349</v>
       </c>
       <c r="D89" s="25" t="s">
         <v>27</v>
@@ -7120,13 +7120,13 @@
     </row>
     <row r="90" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A90" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="B90" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="B90" s="32" t="s">
+      <c r="C90" s="25" t="s">
         <v>351</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>352</v>
       </c>
       <c r="D90" s="25" t="s">
         <v>27</v>
@@ -7143,13 +7143,13 @@
     </row>
     <row r="91" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="B91" s="32" t="s">
         <v>353</v>
       </c>
-      <c r="B91" s="32" t="s">
+      <c r="C91" s="25" t="s">
         <v>354</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>355</v>
       </c>
       <c r="D91" s="25" t="s">
         <v>28</v>
@@ -7166,13 +7166,13 @@
     </row>
     <row r="92" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A92" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>353</v>
+      </c>
+      <c r="C92" s="25" t="s">
         <v>356</v>
-      </c>
-      <c r="B92" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="C92" s="25" t="s">
-        <v>357</v>
       </c>
       <c r="D92" s="25" t="s">
         <v>27</v>
@@ -7187,18 +7187,18 @@
         <v>93</v>
       </c>
       <c r="R92" s="27" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>353</v>
+      </c>
+      <c r="C93" s="25" t="s">
         <v>358</v>
-      </c>
-      <c r="B93" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="C93" s="25" t="s">
-        <v>359</v>
       </c>
       <c r="D93" s="25" t="s">
         <v>26</v>
@@ -7215,13 +7215,13 @@
     </row>
     <row r="94" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A94" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D94" s="25" t="s">
         <v>27</v>
@@ -7236,7 +7236,7 @@
         <v>93</v>
       </c>
       <c r="R94" s="27" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="S94" s="27" t="s">
         <v>68</v>
@@ -7244,13 +7244,13 @@
     </row>
     <row r="95" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A95" s="25" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D95" s="25" t="s">
         <v>27</v>
@@ -7265,7 +7265,7 @@
         <v>93</v>
       </c>
       <c r="R95" s="27" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="S95" s="27" t="s">
         <v>68</v>
@@ -7273,13 +7273,13 @@
     </row>
     <row r="96" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="32" t="s">
         <v>361</v>
       </c>
-      <c r="B96" s="32" t="s">
-        <v>362</v>
-      </c>
       <c r="C96" s="25" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D96" s="25" t="s">
         <v>27</v>
@@ -7291,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="P96" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="R96" s="27" t="s">
         <v>65</v>
@@ -7299,13 +7299,13 @@
     </row>
     <row r="97" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="B97" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="B97" s="32" t="s">
+      <c r="C97" s="25" t="s">
         <v>366</v>
-      </c>
-      <c r="C97" s="25" t="s">
-        <v>367</v>
       </c>
       <c r="D97" s="25" t="s">
         <v>27</v>
@@ -7322,13 +7322,13 @@
     </row>
     <row r="98" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="B98" s="32" t="s">
         <v>368</v>
       </c>
-      <c r="B98" s="32" t="s">
+      <c r="C98" s="25" t="s">
         <v>369</v>
-      </c>
-      <c r="C98" s="25" t="s">
-        <v>370</v>
       </c>
       <c r="D98" s="25" t="s">
         <v>28</v>
@@ -7345,13 +7345,13 @@
     </row>
     <row r="99" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A99" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="B99" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="B99" s="32" t="s">
+      <c r="C99" s="25" t="s">
         <v>372</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>373</v>
       </c>
       <c r="D99" s="25" t="s">
         <v>28</v>
@@ -7368,13 +7368,13 @@
     </row>
     <row r="100" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="B100" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="B100" s="32" t="s">
+      <c r="C100" s="25" t="s">
         <v>375</v>
-      </c>
-      <c r="C100" s="25" t="s">
-        <v>376</v>
       </c>
       <c r="D100" s="25" t="s">
         <v>27</v>
@@ -7389,7 +7389,7 @@
         <v>97</v>
       </c>
       <c r="R100" s="27" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="S100" s="27" t="s">
         <v>68</v>
@@ -7397,13 +7397,13 @@
     </row>
     <row r="101" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="B101" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="B101" s="32" t="s">
+      <c r="C101" s="25" t="s">
         <v>378</v>
-      </c>
-      <c r="C101" s="25" t="s">
-        <v>379</v>
       </c>
       <c r="D101" s="25" t="s">
         <v>27</v>
@@ -7418,7 +7418,7 @@
         <v>93</v>
       </c>
       <c r="R101" s="27" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="S101" s="27" t="s">
         <v>68</v>
@@ -7426,13 +7426,13 @@
     </row>
     <row r="102" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="C102" s="25" t="s">
         <v>380</v>
-      </c>
-      <c r="B102" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="C102" s="25" t="s">
-        <v>381</v>
       </c>
       <c r="D102" s="25" t="s">
         <v>27</v>
@@ -7447,7 +7447,7 @@
         <v>93</v>
       </c>
       <c r="R102" s="27" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="S102" s="27" t="s">
         <v>68</v>
@@ -7455,13 +7455,13 @@
     </row>
     <row r="103" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A103" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="B103" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="C103" s="25" t="s">
         <v>382</v>
-      </c>
-      <c r="B103" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>383</v>
       </c>
       <c r="D103" s="25" t="s">
         <v>28</v>
@@ -7478,13 +7478,13 @@
     </row>
     <row r="104" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="B104" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="B104" s="32" t="s">
+      <c r="C104" s="25" t="s">
         <v>385</v>
-      </c>
-      <c r="C104" s="25" t="s">
-        <v>386</v>
       </c>
       <c r="D104" s="25" t="s">
         <v>27</v>
@@ -7504,13 +7504,13 @@
     </row>
     <row r="105" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A105" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="B105" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="B105" s="32" t="s">
+      <c r="C105" s="25" t="s">
         <v>388</v>
-      </c>
-      <c r="C105" s="25" t="s">
-        <v>389</v>
       </c>
       <c r="D105" s="25" t="s">
         <v>27</v>
@@ -7527,13 +7527,13 @@
     </row>
     <row r="106" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A106" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="B106" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="B106" s="32" t="s">
+      <c r="C106" s="25" t="s">
         <v>391</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>392</v>
       </c>
       <c r="D106" s="25" t="s">
         <v>26</v>
@@ -7550,13 +7550,13 @@
     </row>
     <row r="107" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A107" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B107" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="B107" s="32" t="s">
+      <c r="C107" s="25" t="s">
         <v>394</v>
-      </c>
-      <c r="C107" s="25" t="s">
-        <v>395</v>
       </c>
       <c r="D107" s="25" t="s">
         <v>28</v>
@@ -7573,13 +7573,13 @@
     </row>
     <row r="108" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A108" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="B108" s="32" t="s">
         <v>396</v>
       </c>
-      <c r="B108" s="32" t="s">
+      <c r="C108" s="25" t="s">
         <v>397</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>398</v>
       </c>
       <c r="D108" s="25" t="s">
         <v>27</v>
@@ -7599,13 +7599,13 @@
     </row>
     <row r="109" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A109" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="B109" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="B109" s="32" t="s">
+      <c r="C109" s="25" t="s">
         <v>400</v>
-      </c>
-      <c r="C109" s="25" t="s">
-        <v>401</v>
       </c>
       <c r="D109" s="25" t="s">
         <v>30</v>
@@ -7625,13 +7625,13 @@
     </row>
     <row r="110" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A110" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B110" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="B110" s="32" t="s">
+      <c r="C110" s="25" t="s">
         <v>403</v>
-      </c>
-      <c r="C110" s="25" t="s">
-        <v>404</v>
       </c>
       <c r="D110" s="25" t="s">
         <v>27</v>
@@ -7648,13 +7648,13 @@
     </row>
     <row r="111" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A111" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="B111" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="B111" s="32" t="s">
+      <c r="C111" s="25" t="s">
         <v>406</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>407</v>
       </c>
       <c r="D111" s="25" t="s">
         <v>27</v>
@@ -7671,13 +7671,13 @@
     </row>
     <row r="112" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="B112" s="32" t="s">
         <v>408</v>
       </c>
-      <c r="B112" s="32" t="s">
+      <c r="C112" s="25" t="s">
         <v>409</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>410</v>
       </c>
       <c r="D112" s="25" t="s">
         <v>26</v>
@@ -7694,13 +7694,13 @@
     </row>
     <row r="113" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="B113" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="B113" s="32" t="s">
+      <c r="C113" s="25" t="s">
         <v>412</v>
-      </c>
-      <c r="C113" s="25" t="s">
-        <v>413</v>
       </c>
       <c r="D113" s="25" t="s">
         <v>26</v>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="114" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="25" t="s">
+        <v>413</v>
+      </c>
+      <c r="B114" s="32" t="s">
         <v>414</v>
-      </c>
-      <c r="B114" s="32" t="s">
-        <v>415</v>
       </c>
       <c r="C114" s="25" t="s">
         <v>70</v>
@@ -7740,13 +7740,13 @@
     </row>
     <row r="115" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A115" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="B115" s="32" t="s">
         <v>416</v>
       </c>
-      <c r="B115" s="32" t="s">
+      <c r="C115" s="25" t="s">
         <v>417</v>
-      </c>
-      <c r="C115" s="25" t="s">
-        <v>418</v>
       </c>
       <c r="D115" s="25" t="s">
         <v>26</v>
@@ -7763,13 +7763,13 @@
     </row>
     <row r="116" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A116" s="25" t="s">
+        <v>418</v>
+      </c>
+      <c r="B116" s="32" t="s">
         <v>419</v>
       </c>
-      <c r="B116" s="32" t="s">
+      <c r="C116" s="25" t="s">
         <v>420</v>
-      </c>
-      <c r="C116" s="25" t="s">
-        <v>421</v>
       </c>
       <c r="D116" s="25" t="s">
         <v>26</v>
@@ -7786,13 +7786,13 @@
     </row>
     <row r="117" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A117" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="B117" s="32" t="s">
         <v>422</v>
       </c>
-      <c r="B117" s="32" t="s">
+      <c r="C117" s="25" t="s">
         <v>423</v>
-      </c>
-      <c r="C117" s="25" t="s">
-        <v>424</v>
       </c>
       <c r="D117" s="25" t="s">
         <v>27</v>
@@ -7809,13 +7809,13 @@
     </row>
     <row r="118" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A118" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="B118" s="32" t="s">
         <v>425</v>
       </c>
-      <c r="B118" s="32" t="s">
+      <c r="C118" s="25" t="s">
         <v>426</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>427</v>
       </c>
       <c r="D118" s="25" t="s">
         <v>26</v>
@@ -7832,13 +7832,13 @@
     </row>
     <row r="119" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A119" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="B119" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="B119" s="32" t="s">
+      <c r="C119" s="25" t="s">
         <v>429</v>
-      </c>
-      <c r="C119" s="25" t="s">
-        <v>430</v>
       </c>
       <c r="D119" s="25" t="s">
         <v>28</v>
@@ -7855,13 +7855,13 @@
     </row>
     <row r="120" spans="1:19" ht="153" x14ac:dyDescent="0.2">
       <c r="A120" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="B120" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="B120" s="32" t="s">
+      <c r="C120" s="25" t="s">
         <v>432</v>
-      </c>
-      <c r="C120" s="25" t="s">
-        <v>433</v>
       </c>
       <c r="D120" s="25" t="s">
         <v>30</v>
@@ -7878,13 +7878,13 @@
     </row>
     <row r="121" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A121" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="B121" s="32" t="s">
         <v>434</v>
       </c>
-      <c r="B121" s="32" t="s">
+      <c r="C121" s="25" t="s">
         <v>435</v>
-      </c>
-      <c r="C121" s="25" t="s">
-        <v>436</v>
       </c>
       <c r="D121" s="25" t="s">
         <v>27</v>
@@ -7899,7 +7899,7 @@
         <v>93</v>
       </c>
       <c r="R121" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S121" s="27" t="s">
         <v>68</v>
@@ -7907,13 +7907,13 @@
     </row>
     <row r="122" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="B122" s="32" t="s">
         <v>437</v>
       </c>
-      <c r="B122" s="32" t="s">
+      <c r="C122" s="25" t="s">
         <v>438</v>
-      </c>
-      <c r="C122" s="25" t="s">
-        <v>439</v>
       </c>
       <c r="D122" s="25" t="s">
         <v>27</v>
@@ -7928,7 +7928,7 @@
         <v>93</v>
       </c>
       <c r="R122" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S122" s="27" t="s">
         <v>68</v>
@@ -7936,13 +7936,13 @@
     </row>
     <row r="123" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="B123" s="32" t="s">
         <v>440</v>
       </c>
-      <c r="B123" s="32" t="s">
+      <c r="C123" s="25" t="s">
         <v>441</v>
-      </c>
-      <c r="C123" s="25" t="s">
-        <v>442</v>
       </c>
       <c r="D123" s="25" t="s">
         <v>30</v>
@@ -7959,13 +7959,13 @@
     </row>
     <row r="124" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A124" s="25" t="s">
+        <v>442</v>
+      </c>
+      <c r="B124" s="32" t="s">
         <v>443</v>
       </c>
-      <c r="B124" s="32" t="s">
+      <c r="C124" s="25" t="s">
         <v>444</v>
-      </c>
-      <c r="C124" s="25" t="s">
-        <v>445</v>
       </c>
       <c r="D124" s="25" t="s">
         <v>27</v>
@@ -7982,13 +7982,13 @@
     </row>
     <row r="125" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A125" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="B125" s="32" t="s">
         <v>446</v>
       </c>
-      <c r="B125" s="32" t="s">
+      <c r="C125" s="25" t="s">
         <v>447</v>
-      </c>
-      <c r="C125" s="25" t="s">
-        <v>448</v>
       </c>
       <c r="D125" s="25" t="s">
         <v>27</v>
@@ -8003,7 +8003,7 @@
         <v>93</v>
       </c>
       <c r="R125" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S125" s="27" t="s">
         <v>68</v>
@@ -8011,13 +8011,13 @@
     </row>
     <row r="126" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A126" s="25" t="s">
+        <v>448</v>
+      </c>
+      <c r="B126" s="32" t="s">
         <v>449</v>
       </c>
-      <c r="B126" s="32" t="s">
+      <c r="C126" s="25" t="s">
         <v>450</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>451</v>
       </c>
       <c r="D126" s="25" t="s">
         <v>26</v>
@@ -8034,13 +8034,13 @@
     </row>
     <row r="127" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A127" s="25" t="s">
+        <v>451</v>
+      </c>
+      <c r="B127" s="32" t="s">
         <v>452</v>
       </c>
-      <c r="B127" s="32" t="s">
-        <v>453</v>
-      </c>
       <c r="C127" s="25" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D127" s="25" t="s">
         <v>27</v>
@@ -8052,10 +8052,10 @@
         <v>0</v>
       </c>
       <c r="P127" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R127" s="27" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="S127" s="27" t="s">
         <v>68</v>
@@ -8063,13 +8063,13 @@
     </row>
     <row r="128" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A128" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="B128" s="32" t="s">
         <v>456</v>
       </c>
-      <c r="B128" s="32" t="s">
+      <c r="C128" s="25" t="s">
         <v>457</v>
-      </c>
-      <c r="C128" s="25" t="s">
-        <v>458</v>
       </c>
       <c r="D128" s="25" t="s">
         <v>27</v>
@@ -8084,7 +8084,7 @@
         <v>93</v>
       </c>
       <c r="R128" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S128" s="27" t="s">
         <v>68</v>
@@ -8092,13 +8092,13 @@
     </row>
     <row r="129" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A129" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="B129" s="32" t="s">
         <v>459</v>
       </c>
-      <c r="B129" s="32" t="s">
+      <c r="C129" s="25" t="s">
         <v>460</v>
-      </c>
-      <c r="C129" s="25" t="s">
-        <v>461</v>
       </c>
       <c r="D129" s="25" t="s">
         <v>26</v>
@@ -8115,13 +8115,13 @@
     </row>
     <row r="130" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A130" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="B130" s="32" t="s">
         <v>462</v>
       </c>
-      <c r="B130" s="32" t="s">
+      <c r="C130" s="25" t="s">
         <v>463</v>
-      </c>
-      <c r="C130" s="25" t="s">
-        <v>464</v>
       </c>
       <c r="D130" s="25" t="s">
         <v>27</v>
@@ -8136,7 +8136,7 @@
         <v>93</v>
       </c>
       <c r="R130" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S130" s="27" t="s">
         <v>68</v>
@@ -8144,13 +8144,13 @@
     </row>
     <row r="131" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A131" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="B131" s="32" t="s">
         <v>465</v>
       </c>
-      <c r="B131" s="32" t="s">
+      <c r="C131" s="25" t="s">
         <v>466</v>
-      </c>
-      <c r="C131" s="25" t="s">
-        <v>467</v>
       </c>
       <c r="D131" s="25" t="s">
         <v>28</v>
@@ -8167,13 +8167,13 @@
     </row>
     <row r="132" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A132" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="B132" s="32" t="s">
         <v>468</v>
       </c>
-      <c r="B132" s="32" t="s">
+      <c r="C132" s="25" t="s">
         <v>469</v>
-      </c>
-      <c r="C132" s="25" t="s">
-        <v>470</v>
       </c>
       <c r="D132" s="25" t="s">
         <v>27</v>
@@ -8188,7 +8188,7 @@
         <v>93</v>
       </c>
       <c r="R132" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S132" s="27" t="s">
         <v>68</v>
@@ -8196,13 +8196,13 @@
     </row>
     <row r="133" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A133" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="B133" s="32" t="s">
         <v>471</v>
       </c>
-      <c r="B133" s="32" t="s">
+      <c r="C133" s="25" t="s">
         <v>472</v>
-      </c>
-      <c r="C133" s="25" t="s">
-        <v>473</v>
       </c>
       <c r="D133" s="25" t="s">
         <v>26</v>
@@ -8219,13 +8219,13 @@
     </row>
     <row r="134" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A134" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="B134" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="B134" s="32" t="s">
+      <c r="C134" s="25" t="s">
         <v>475</v>
-      </c>
-      <c r="C134" s="25" t="s">
-        <v>476</v>
       </c>
       <c r="D134" s="25" t="s">
         <v>27</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="P134" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R134" s="27" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="S134" s="27" t="s">
         <v>68</v>
@@ -8248,13 +8248,13 @@
     </row>
     <row r="135" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A135" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="B135" s="32" t="s">
         <v>477</v>
       </c>
-      <c r="B135" s="32" t="s">
+      <c r="C135" s="25" t="s">
         <v>478</v>
-      </c>
-      <c r="C135" s="25" t="s">
-        <v>479</v>
       </c>
       <c r="D135" s="25" t="s">
         <v>28</v>
@@ -8271,13 +8271,13 @@
     </row>
     <row r="136" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A136" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="B136" s="32" t="s">
         <v>480</v>
       </c>
-      <c r="B136" s="32" t="s">
+      <c r="C136" s="25" t="s">
         <v>481</v>
-      </c>
-      <c r="C136" s="25" t="s">
-        <v>482</v>
       </c>
       <c r="D136" s="25" t="s">
         <v>27</v>
@@ -8292,7 +8292,7 @@
         <v>93</v>
       </c>
       <c r="R136" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S136" s="27" t="s">
         <v>68</v>
@@ -8300,13 +8300,13 @@
     </row>
     <row r="137" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A137" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="B137" s="32" t="s">
         <v>483</v>
       </c>
-      <c r="B137" s="32" t="s">
+      <c r="C137" s="25" t="s">
         <v>484</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>485</v>
       </c>
       <c r="D137" s="25" t="s">
         <v>26</v>
@@ -8323,13 +8323,13 @@
     </row>
     <row r="138" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A138" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="B138" s="32" t="s">
         <v>486</v>
       </c>
-      <c r="B138" s="32" t="s">
+      <c r="C138" s="25" t="s">
         <v>487</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>488</v>
       </c>
       <c r="D138" s="25" t="s">
         <v>27</v>
@@ -8344,7 +8344,7 @@
         <v>93</v>
       </c>
       <c r="R138" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S138" s="27" t="s">
         <v>68</v>
@@ -8352,13 +8352,13 @@
     </row>
     <row r="139" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A139" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="B139" s="32" t="s">
         <v>489</v>
       </c>
-      <c r="B139" s="32" t="s">
+      <c r="C139" s="25" t="s">
         <v>490</v>
-      </c>
-      <c r="C139" s="25" t="s">
-        <v>491</v>
       </c>
       <c r="D139" s="25" t="s">
         <v>26</v>
@@ -8375,13 +8375,13 @@
     </row>
     <row r="140" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A140" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="B140" s="32" t="s">
         <v>492</v>
       </c>
-      <c r="B140" s="32" t="s">
-        <v>493</v>
-      </c>
       <c r="C140" s="25" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D140" s="25" t="s">
         <v>27</v>
@@ -8393,10 +8393,10 @@
         <v>0</v>
       </c>
       <c r="P140" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R140" s="27" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="S140" s="27" t="s">
         <v>68</v>
@@ -8404,13 +8404,13 @@
     </row>
     <row r="141" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A141" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="B141" s="32" t="s">
         <v>494</v>
       </c>
-      <c r="B141" s="32" t="s">
+      <c r="C141" s="25" t="s">
         <v>495</v>
-      </c>
-      <c r="C141" s="25" t="s">
-        <v>496</v>
       </c>
       <c r="D141" s="25" t="s">
         <v>27</v>
@@ -8430,13 +8430,13 @@
     </row>
     <row r="142" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A142" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="B142" s="32" t="s">
         <v>497</v>
       </c>
-      <c r="B142" s="32" t="s">
+      <c r="C142" s="25" t="s">
         <v>498</v>
-      </c>
-      <c r="C142" s="25" t="s">
-        <v>499</v>
       </c>
       <c r="D142" s="25" t="s">
         <v>28</v>
@@ -8453,13 +8453,13 @@
     </row>
     <row r="143" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A143" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="B143" s="32" t="s">
         <v>500</v>
       </c>
-      <c r="B143" s="32" t="s">
+      <c r="C143" s="25" t="s">
         <v>501</v>
-      </c>
-      <c r="C143" s="25" t="s">
-        <v>502</v>
       </c>
       <c r="D143" s="25" t="s">
         <v>27</v>
@@ -8474,7 +8474,7 @@
         <v>93</v>
       </c>
       <c r="R143" s="27" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="S143" s="27" t="s">
         <v>68</v>
@@ -8482,13 +8482,13 @@
     </row>
     <row r="144" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A144" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="B144" s="32" t="s">
         <v>503</v>
       </c>
-      <c r="B144" s="32" t="s">
+      <c r="C144" s="25" t="s">
         <v>504</v>
-      </c>
-      <c r="C144" s="25" t="s">
-        <v>505</v>
       </c>
       <c r="D144" s="25" t="s">
         <v>26</v>
@@ -8505,13 +8505,13 @@
     </row>
     <row r="145" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A145" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="B145" s="32" t="s">
         <v>506</v>
       </c>
-      <c r="B145" s="32" t="s">
+      <c r="C145" s="25" t="s">
         <v>507</v>
-      </c>
-      <c r="C145" s="25" t="s">
-        <v>508</v>
       </c>
       <c r="D145" s="25" t="s">
         <v>28</v>
@@ -8528,13 +8528,13 @@
     </row>
     <row r="146" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A146" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="B146" s="32" t="s">
         <v>509</v>
       </c>
-      <c r="B146" s="32" t="s">
+      <c r="C146" s="25" t="s">
         <v>510</v>
-      </c>
-      <c r="C146" s="25" t="s">
-        <v>511</v>
       </c>
       <c r="D146" s="25" t="s">
         <v>28</v>
@@ -8546,18 +8546,18 @@
         <v>0</v>
       </c>
       <c r="P146" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="147" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="B147" s="32" t="s">
         <v>512</v>
       </c>
-      <c r="B147" s="32" t="s">
+      <c r="C147" s="25" t="s">
         <v>513</v>
-      </c>
-      <c r="C147" s="25" t="s">
-        <v>514</v>
       </c>
       <c r="D147" s="25" t="s">
         <v>28</v>
@@ -8574,13 +8574,13 @@
     </row>
     <row r="148" spans="1:21" ht="187" x14ac:dyDescent="0.2">
       <c r="A148" s="25" t="s">
+        <v>514</v>
+      </c>
+      <c r="B148" s="32" t="s">
         <v>515</v>
       </c>
-      <c r="B148" s="32" t="s">
-        <v>516</v>
-      </c>
       <c r="C148" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D148" s="25" t="s">
         <v>27</v>
@@ -8595,24 +8595,24 @@
         <v>93</v>
       </c>
       <c r="R148" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S148" s="27" t="s">
         <v>68</v>
       </c>
       <c r="U148" s="27" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="149" spans="1:21" ht="170" x14ac:dyDescent="0.2">
       <c r="A149" s="25" t="s">
+        <v>516</v>
+      </c>
+      <c r="B149" s="32" t="s">
         <v>517</v>
       </c>
-      <c r="B149" s="32" t="s">
-        <v>518</v>
-      </c>
       <c r="C149" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D149" s="25" t="s">
         <v>27</v>
@@ -8627,21 +8627,21 @@
         <v>93</v>
       </c>
       <c r="R149" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S149" s="27" t="s">
         <v>68</v>
       </c>
       <c r="U149" s="27" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="150" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A150" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="B150" s="32" t="s">
         <v>519</v>
-      </c>
-      <c r="B150" s="32" t="s">
-        <v>520</v>
       </c>
       <c r="C150" s="25" t="s">
         <v>71</v>
@@ -8659,7 +8659,7 @@
         <v>93</v>
       </c>
       <c r="R150" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S150" s="27" t="s">
         <v>68</v>
@@ -8667,13 +8667,13 @@
     </row>
     <row r="151" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A151" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="B151" s="32" t="s">
         <v>521</v>
       </c>
-      <c r="B151" s="32" t="s">
+      <c r="C151" s="25" t="s">
         <v>522</v>
-      </c>
-      <c r="C151" s="25" t="s">
-        <v>523</v>
       </c>
       <c r="D151" s="25" t="s">
         <v>27</v>
@@ -8688,7 +8688,7 @@
         <v>93</v>
       </c>
       <c r="R151" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S151" s="27" t="s">
         <v>68</v>
@@ -8696,13 +8696,13 @@
     </row>
     <row r="152" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A152" s="25" t="s">
+        <v>523</v>
+      </c>
+      <c r="B152" s="32" t="s">
         <v>524</v>
       </c>
-      <c r="B152" s="32" t="s">
+      <c r="C152" s="25" t="s">
         <v>525</v>
-      </c>
-      <c r="C152" s="25" t="s">
-        <v>526</v>
       </c>
       <c r="D152" s="25" t="s">
         <v>27</v>
@@ -8717,7 +8717,7 @@
         <v>93</v>
       </c>
       <c r="R152" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S152" s="27" t="s">
         <v>68</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="153" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A153" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="B153" s="32" t="s">
         <v>527</v>
-      </c>
-      <c r="B153" s="32" t="s">
-        <v>528</v>
       </c>
       <c r="C153" s="25" t="s">
         <v>72</v>
@@ -8746,7 +8746,7 @@
         <v>93</v>
       </c>
       <c r="R153" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S153" s="27" t="s">
         <v>68</v>
@@ -8754,10 +8754,10 @@
     </row>
     <row r="154" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A154" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B154" s="32" t="s">
         <v>529</v>
-      </c>
-      <c r="B154" s="32" t="s">
-        <v>530</v>
       </c>
       <c r="C154" s="25" t="s">
         <v>73</v>
@@ -8775,7 +8775,7 @@
         <v>93</v>
       </c>
       <c r="R154" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S154" s="27" t="s">
         <v>68</v>
@@ -8783,13 +8783,13 @@
     </row>
     <row r="155" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A155" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="B155" s="32" t="s">
         <v>531</v>
       </c>
-      <c r="B155" s="32" t="s">
+      <c r="C155" s="25" t="s">
         <v>532</v>
-      </c>
-      <c r="C155" s="25" t="s">
-        <v>533</v>
       </c>
       <c r="D155" s="25" t="s">
         <v>27</v>
@@ -8804,7 +8804,7 @@
         <v>93</v>
       </c>
       <c r="R155" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S155" s="27" t="s">
         <v>68</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="156" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A156" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="B156" s="32" t="s">
         <v>534</v>
-      </c>
-      <c r="B156" s="32" t="s">
-        <v>535</v>
       </c>
       <c r="C156" s="25" t="s">
         <v>74</v>
@@ -8833,7 +8833,7 @@
         <v>93</v>
       </c>
       <c r="R156" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S156" s="27" t="s">
         <v>68</v>
@@ -8841,10 +8841,10 @@
     </row>
     <row r="157" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A157" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="B157" s="32" t="s">
         <v>536</v>
-      </c>
-      <c r="B157" s="32" t="s">
-        <v>537</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>75</v>
@@ -8862,7 +8862,7 @@
         <v>93</v>
       </c>
       <c r="R157" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S157" s="27" t="s">
         <v>68</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="158" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A158" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="B158" s="32" t="s">
         <v>538</v>
-      </c>
-      <c r="B158" s="32" t="s">
-        <v>539</v>
       </c>
       <c r="C158" s="25" t="s">
         <v>76</v>
@@ -8891,7 +8891,7 @@
         <v>93</v>
       </c>
       <c r="R158" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S158" s="27" t="s">
         <v>68</v>
@@ -8899,10 +8899,10 @@
     </row>
     <row r="159" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A159" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="B159" s="32" t="s">
         <v>540</v>
-      </c>
-      <c r="B159" s="32" t="s">
-        <v>541</v>
       </c>
       <c r="C159" s="25" t="s">
         <v>77</v>
@@ -8920,7 +8920,7 @@
         <v>93</v>
       </c>
       <c r="R159" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S159" s="27" t="s">
         <v>68</v>
@@ -8928,13 +8928,13 @@
     </row>
     <row r="160" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A160" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="B160" s="32" t="s">
         <v>542</v>
       </c>
-      <c r="B160" s="32" t="s">
+      <c r="C160" s="25" t="s">
         <v>543</v>
-      </c>
-      <c r="C160" s="25" t="s">
-        <v>544</v>
       </c>
       <c r="D160" s="25" t="s">
         <v>27</v>
@@ -8957,13 +8957,13 @@
     </row>
     <row r="161" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A161" s="25" t="s">
+        <v>544</v>
+      </c>
+      <c r="B161" s="32" t="s">
         <v>545</v>
       </c>
-      <c r="B161" s="32" t="s">
+      <c r="C161" s="25" t="s">
         <v>546</v>
-      </c>
-      <c r="C161" s="25" t="s">
-        <v>547</v>
       </c>
       <c r="D161" s="25" t="s">
         <v>26</v>
@@ -8980,13 +8980,13 @@
     </row>
     <row r="162" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A162" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="B162" s="32" t="s">
         <v>548</v>
       </c>
-      <c r="B162" s="32" t="s">
+      <c r="C162" s="25" t="s">
         <v>549</v>
-      </c>
-      <c r="C162" s="25" t="s">
-        <v>550</v>
       </c>
       <c r="D162" s="25" t="s">
         <v>28</v>
@@ -9003,13 +9003,13 @@
     </row>
     <row r="163" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A163" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="B163" s="32" t="s">
         <v>551</v>
       </c>
-      <c r="B163" s="32" t="s">
+      <c r="C163" s="25" t="s">
         <v>552</v>
-      </c>
-      <c r="C163" s="25" t="s">
-        <v>553</v>
       </c>
       <c r="D163" s="25" t="s">
         <v>28</v>
@@ -9026,13 +9026,13 @@
     </row>
     <row r="164" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A164" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="B164" s="32" t="s">
         <v>554</v>
       </c>
-      <c r="B164" s="32" t="s">
+      <c r="C164" s="25" t="s">
         <v>555</v>
-      </c>
-      <c r="C164" s="25" t="s">
-        <v>556</v>
       </c>
       <c r="D164" s="25" t="s">
         <v>28</v>
@@ -9049,13 +9049,13 @@
     </row>
     <row r="165" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A165" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="B165" s="32" t="s">
         <v>557</v>
       </c>
-      <c r="B165" s="32" t="s">
+      <c r="C165" s="25" t="s">
         <v>558</v>
-      </c>
-      <c r="C165" s="25" t="s">
-        <v>559</v>
       </c>
       <c r="D165" s="25" t="s">
         <v>27</v>
@@ -9072,13 +9072,13 @@
     </row>
     <row r="166" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A166" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="B166" s="32" t="s">
         <v>560</v>
       </c>
-      <c r="B166" s="32" t="s">
+      <c r="C166" s="25" t="s">
         <v>561</v>
-      </c>
-      <c r="C166" s="25" t="s">
-        <v>562</v>
       </c>
       <c r="D166" s="25" t="s">
         <v>27</v>
@@ -9095,13 +9095,13 @@
     </row>
     <row r="167" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A167" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="B167" s="32" t="s">
         <v>563</v>
       </c>
-      <c r="B167" s="32" t="s">
+      <c r="C167" s="25" t="s">
         <v>564</v>
-      </c>
-      <c r="C167" s="25" t="s">
-        <v>565</v>
       </c>
       <c r="D167" s="25" t="s">
         <v>27</v>
@@ -9118,13 +9118,13 @@
     </row>
     <row r="168" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A168" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="B168" s="32" t="s">
         <v>566</v>
       </c>
-      <c r="B168" s="32" t="s">
+      <c r="C168" s="25" t="s">
         <v>567</v>
-      </c>
-      <c r="C168" s="25" t="s">
-        <v>568</v>
       </c>
       <c r="D168" s="25" t="s">
         <v>28</v>
@@ -9141,13 +9141,13 @@
     </row>
     <row r="169" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A169" s="25" t="s">
+        <v>568</v>
+      </c>
+      <c r="B169" s="32" t="s">
         <v>569</v>
       </c>
-      <c r="B169" s="32" t="s">
+      <c r="C169" s="25" t="s">
         <v>570</v>
-      </c>
-      <c r="C169" s="25" t="s">
-        <v>571</v>
       </c>
       <c r="D169" s="25" t="s">
         <v>28</v>
@@ -9164,13 +9164,13 @@
     </row>
     <row r="170" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A170" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="B170" s="32" t="s">
         <v>572</v>
       </c>
-      <c r="B170" s="32" t="s">
+      <c r="C170" s="25" t="s">
         <v>573</v>
-      </c>
-      <c r="C170" s="25" t="s">
-        <v>574</v>
       </c>
       <c r="D170" s="25" t="s">
         <v>28</v>
@@ -9187,13 +9187,13 @@
     </row>
     <row r="171" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A171" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="B171" s="32" t="s">
         <v>575</v>
       </c>
-      <c r="B171" s="32" t="s">
+      <c r="C171" s="25" t="s">
         <v>576</v>
-      </c>
-      <c r="C171" s="25" t="s">
-        <v>577</v>
       </c>
       <c r="D171" s="25" t="s">
         <v>28</v>
@@ -9210,13 +9210,13 @@
     </row>
     <row r="172" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A172" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="B172" s="32" t="s">
         <v>578</v>
       </c>
-      <c r="B172" s="32" t="s">
+      <c r="C172" s="25" t="s">
         <v>579</v>
-      </c>
-      <c r="C172" s="25" t="s">
-        <v>580</v>
       </c>
       <c r="D172" s="25" t="s">
         <v>28</v>
@@ -9233,13 +9233,13 @@
     </row>
     <row r="173" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A173" s="25" t="s">
+        <v>580</v>
+      </c>
+      <c r="B173" s="32" t="s">
         <v>581</v>
       </c>
-      <c r="B173" s="32" t="s">
+      <c r="C173" s="25" t="s">
         <v>582</v>
-      </c>
-      <c r="C173" s="25" t="s">
-        <v>583</v>
       </c>
       <c r="D173" s="25" t="s">
         <v>28</v>
@@ -9256,13 +9256,13 @@
     </row>
     <row r="174" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A174" s="25" t="s">
+        <v>583</v>
+      </c>
+      <c r="B174" s="32" t="s">
         <v>584</v>
       </c>
-      <c r="B174" s="32" t="s">
+      <c r="C174" s="25" t="s">
         <v>585</v>
-      </c>
-      <c r="C174" s="25" t="s">
-        <v>586</v>
       </c>
       <c r="D174" s="25" t="s">
         <v>29</v>
@@ -9279,13 +9279,13 @@
     </row>
     <row r="175" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A175" s="25" t="s">
+        <v>586</v>
+      </c>
+      <c r="B175" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="B175" s="32" t="s">
+      <c r="C175" s="25" t="s">
         <v>588</v>
-      </c>
-      <c r="C175" s="25" t="s">
-        <v>589</v>
       </c>
       <c r="D175" s="25" t="s">
         <v>27</v>
@@ -9302,13 +9302,13 @@
     </row>
     <row r="176" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A176" s="25" t="s">
+        <v>589</v>
+      </c>
+      <c r="B176" s="32" t="s">
         <v>590</v>
       </c>
-      <c r="B176" s="32" t="s">
+      <c r="C176" s="25" t="s">
         <v>591</v>
-      </c>
-      <c r="C176" s="25" t="s">
-        <v>592</v>
       </c>
       <c r="D176" s="25" t="s">
         <v>27</v>
@@ -9323,7 +9323,7 @@
         <v>93</v>
       </c>
       <c r="R176" s="27" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="S176" s="27" t="s">
         <v>68</v>
@@ -9331,13 +9331,13 @@
     </row>
     <row r="177" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A177" s="25" t="s">
+        <v>592</v>
+      </c>
+      <c r="B177" s="32" t="s">
         <v>593</v>
       </c>
-      <c r="B177" s="32" t="s">
+      <c r="C177" s="25" t="s">
         <v>594</v>
-      </c>
-      <c r="C177" s="25" t="s">
-        <v>595</v>
       </c>
       <c r="D177" s="25" t="s">
         <v>28</v>
@@ -9354,13 +9354,13 @@
     </row>
     <row r="178" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A178" s="25" t="s">
+        <v>595</v>
+      </c>
+      <c r="B178" s="32" t="s">
         <v>596</v>
       </c>
-      <c r="B178" s="32" t="s">
+      <c r="C178" s="25" t="s">
         <v>597</v>
-      </c>
-      <c r="C178" s="25" t="s">
-        <v>598</v>
       </c>
       <c r="D178" s="25" t="s">
         <v>28</v>
@@ -9377,13 +9377,13 @@
     </row>
     <row r="179" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A179" s="25" t="s">
+        <v>598</v>
+      </c>
+      <c r="B179" s="32" t="s">
         <v>599</v>
       </c>
-      <c r="B179" s="32" t="s">
+      <c r="C179" s="25" t="s">
         <v>600</v>
-      </c>
-      <c r="C179" s="25" t="s">
-        <v>601</v>
       </c>
       <c r="D179" s="25" t="s">
         <v>30</v>
@@ -9400,13 +9400,13 @@
     </row>
     <row r="180" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A180" s="25" t="s">
+        <v>601</v>
+      </c>
+      <c r="B180" s="32" t="s">
         <v>602</v>
       </c>
-      <c r="B180" s="32" t="s">
+      <c r="C180" s="25" t="s">
         <v>603</v>
-      </c>
-      <c r="C180" s="25" t="s">
-        <v>604</v>
       </c>
       <c r="D180" s="25" t="s">
         <v>27</v>
@@ -9423,13 +9423,13 @@
     </row>
     <row r="181" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A181" s="25" t="s">
+        <v>604</v>
+      </c>
+      <c r="B181" s="32" t="s">
         <v>605</v>
       </c>
-      <c r="B181" s="32" t="s">
+      <c r="C181" s="25" t="s">
         <v>606</v>
-      </c>
-      <c r="C181" s="25" t="s">
-        <v>607</v>
       </c>
       <c r="D181" s="25" t="s">
         <v>27</v>
@@ -9446,13 +9446,13 @@
     </row>
     <row r="182" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A182" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="B182" s="32" t="s">
         <v>608</v>
       </c>
-      <c r="B182" s="32" t="s">
+      <c r="C182" s="25" t="s">
         <v>609</v>
-      </c>
-      <c r="C182" s="25" t="s">
-        <v>610</v>
       </c>
       <c r="D182" s="25" t="s">
         <v>28</v>
@@ -9469,13 +9469,13 @@
     </row>
     <row r="183" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A183" s="25" t="s">
+        <v>610</v>
+      </c>
+      <c r="B183" s="32" t="s">
         <v>611</v>
       </c>
-      <c r="B183" s="32" t="s">
+      <c r="C183" s="25" t="s">
         <v>612</v>
-      </c>
-      <c r="C183" s="25" t="s">
-        <v>613</v>
       </c>
       <c r="D183" s="25" t="s">
         <v>28</v>
@@ -9492,13 +9492,13 @@
     </row>
     <row r="184" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A184" s="25" t="s">
+        <v>613</v>
+      </c>
+      <c r="B184" s="32" t="s">
         <v>614</v>
       </c>
-      <c r="B184" s="32" t="s">
+      <c r="C184" s="25" t="s">
         <v>615</v>
-      </c>
-      <c r="C184" s="25" t="s">
-        <v>616</v>
       </c>
       <c r="D184" s="25" t="s">
         <v>27</v>
@@ -9515,13 +9515,13 @@
     </row>
     <row r="185" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A185" s="25" t="s">
+        <v>616</v>
+      </c>
+      <c r="B185" s="32" t="s">
         <v>617</v>
       </c>
-      <c r="B185" s="32" t="s">
+      <c r="C185" s="25" t="s">
         <v>618</v>
-      </c>
-      <c r="C185" s="25" t="s">
-        <v>619</v>
       </c>
       <c r="D185" s="25" t="s">
         <v>30</v>
@@ -9538,13 +9538,13 @@
     </row>
     <row r="186" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A186" s="25" t="s">
+        <v>619</v>
+      </c>
+      <c r="B186" s="32" t="s">
         <v>620</v>
       </c>
-      <c r="B186" s="32" t="s">
+      <c r="C186" s="25" t="s">
         <v>621</v>
-      </c>
-      <c r="C186" s="25" t="s">
-        <v>622</v>
       </c>
       <c r="D186" s="25" t="s">
         <v>27</v>
@@ -9561,13 +9561,13 @@
     </row>
     <row r="187" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A187" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="B187" s="32" t="s">
         <v>623</v>
       </c>
-      <c r="B187" s="32" t="s">
+      <c r="C187" s="25" t="s">
         <v>624</v>
-      </c>
-      <c r="C187" s="25" t="s">
-        <v>625</v>
       </c>
       <c r="D187" s="25" t="s">
         <v>30</v>
@@ -9584,13 +9584,13 @@
     </row>
     <row r="188" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A188" s="25" t="s">
+        <v>625</v>
+      </c>
+      <c r="B188" s="32" t="s">
         <v>626</v>
       </c>
-      <c r="B188" s="32" t="s">
+      <c r="C188" s="25" t="s">
         <v>627</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>628</v>
       </c>
       <c r="D188" s="25" t="s">
         <v>27</v>
@@ -9607,13 +9607,13 @@
     </row>
     <row r="189" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A189" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="B189" s="32" t="s">
         <v>629</v>
       </c>
-      <c r="B189" s="32" t="s">
+      <c r="C189" s="25" t="s">
         <v>630</v>
-      </c>
-      <c r="C189" s="25" t="s">
-        <v>631</v>
       </c>
       <c r="D189" s="25" t="s">
         <v>26</v>
@@ -9631,13 +9631,13 @@
     </row>
     <row r="190" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A190" s="25" t="s">
+        <v>631</v>
+      </c>
+      <c r="B190" s="32" t="s">
         <v>632</v>
       </c>
-      <c r="B190" s="32" t="s">
+      <c r="C190" s="25" t="s">
         <v>633</v>
-      </c>
-      <c r="C190" s="25" t="s">
-        <v>634</v>
       </c>
       <c r="D190" s="25" t="s">
         <v>27</v>
@@ -9654,13 +9654,13 @@
     </row>
     <row r="191" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A191" s="25" t="s">
+        <v>634</v>
+      </c>
+      <c r="B191" s="32" t="s">
         <v>635</v>
       </c>
-      <c r="B191" s="32" t="s">
+      <c r="C191" s="25" t="s">
         <v>636</v>
-      </c>
-      <c r="C191" s="25" t="s">
-        <v>637</v>
       </c>
       <c r="D191" s="25" t="s">
         <v>27</v>
@@ -9677,13 +9677,13 @@
     </row>
     <row r="192" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A192" s="25" t="s">
+        <v>637</v>
+      </c>
+      <c r="B192" s="32" t="s">
         <v>638</v>
       </c>
-      <c r="B192" s="32" t="s">
+      <c r="C192" s="25" t="s">
         <v>639</v>
-      </c>
-      <c r="C192" s="25" t="s">
-        <v>640</v>
       </c>
       <c r="D192" s="25" t="s">
         <v>27</v>
@@ -9700,13 +9700,13 @@
     </row>
     <row r="193" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A193" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="B193" s="32" t="s">
         <v>641</v>
       </c>
-      <c r="B193" s="32" t="s">
+      <c r="C193" s="25" t="s">
         <v>642</v>
-      </c>
-      <c r="C193" s="25" t="s">
-        <v>643</v>
       </c>
       <c r="D193" s="25" t="s">
         <v>27</v>
@@ -9726,13 +9726,13 @@
     </row>
     <row r="194" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A194" s="25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B194" s="32" t="s">
         <v>644</v>
       </c>
-      <c r="B194" s="32" t="s">
+      <c r="C194" s="25" t="s">
         <v>645</v>
-      </c>
-      <c r="C194" s="25" t="s">
-        <v>646</v>
       </c>
       <c r="D194" s="25" t="s">
         <v>27</v>
@@ -9749,13 +9749,13 @@
     </row>
     <row r="195" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="25" t="s">
+        <v>646</v>
+      </c>
+      <c r="B195" s="32" t="s">
         <v>647</v>
       </c>
-      <c r="B195" s="32" t="s">
+      <c r="C195" s="25" t="s">
         <v>648</v>
-      </c>
-      <c r="C195" s="25" t="s">
-        <v>649</v>
       </c>
       <c r="D195" s="25" t="s">
         <v>26</v>
@@ -9772,13 +9772,13 @@
     </row>
     <row r="196" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A196" s="25" t="s">
+        <v>649</v>
+      </c>
+      <c r="B196" s="32" t="s">
         <v>650</v>
       </c>
-      <c r="B196" s="32" t="s">
+      <c r="C196" s="25" t="s">
         <v>651</v>
-      </c>
-      <c r="C196" s="25" t="s">
-        <v>652</v>
       </c>
       <c r="D196" s="25" t="s">
         <v>26</v>
@@ -9795,13 +9795,13 @@
     </row>
     <row r="197" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A197" s="25" t="s">
+        <v>652</v>
+      </c>
+      <c r="B197" s="32" t="s">
         <v>653</v>
       </c>
-      <c r="B197" s="32" t="s">
+      <c r="C197" s="25" t="s">
         <v>654</v>
-      </c>
-      <c r="C197" s="25" t="s">
-        <v>655</v>
       </c>
       <c r="D197" s="25" t="s">
         <v>30</v>
@@ -9818,13 +9818,13 @@
     </row>
     <row r="198" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A198" s="25" t="s">
+        <v>655</v>
+      </c>
+      <c r="B198" s="32" t="s">
         <v>656</v>
       </c>
-      <c r="B198" s="32" t="s">
+      <c r="C198" s="25" t="s">
         <v>657</v>
-      </c>
-      <c r="C198" s="25" t="s">
-        <v>658</v>
       </c>
       <c r="D198" s="25" t="s">
         <v>28</v>
@@ -9841,13 +9841,13 @@
     </row>
     <row r="199" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A199" s="25" t="s">
+        <v>658</v>
+      </c>
+      <c r="B199" s="32" t="s">
         <v>659</v>
       </c>
-      <c r="B199" s="32" t="s">
+      <c r="C199" s="25" t="s">
         <v>660</v>
-      </c>
-      <c r="C199" s="25" t="s">
-        <v>661</v>
       </c>
       <c r="D199" s="25" t="s">
         <v>30</v>
@@ -9864,13 +9864,13 @@
     </row>
     <row r="200" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A200" s="25" t="s">
+        <v>661</v>
+      </c>
+      <c r="B200" s="32" t="s">
         <v>662</v>
       </c>
-      <c r="B200" s="32" t="s">
+      <c r="C200" s="25" t="s">
         <v>663</v>
-      </c>
-      <c r="C200" s="25" t="s">
-        <v>664</v>
       </c>
       <c r="D200" s="25" t="s">
         <v>28</v>
@@ -9887,13 +9887,13 @@
     </row>
     <row r="201" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A201" s="25" t="s">
+        <v>664</v>
+      </c>
+      <c r="B201" s="32" t="s">
         <v>665</v>
       </c>
-      <c r="B201" s="32" t="s">
+      <c r="C201" s="25" t="s">
         <v>666</v>
-      </c>
-      <c r="C201" s="25" t="s">
-        <v>667</v>
       </c>
       <c r="D201" s="25" t="s">
         <v>28</v>
@@ -9910,13 +9910,13 @@
     </row>
     <row r="202" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A202" s="25" t="s">
+        <v>667</v>
+      </c>
+      <c r="B202" s="32" t="s">
         <v>668</v>
       </c>
-      <c r="B202" s="32" t="s">
+      <c r="C202" s="25" t="s">
         <v>669</v>
-      </c>
-      <c r="C202" s="25" t="s">
-        <v>670</v>
       </c>
       <c r="D202" s="25" t="s">
         <v>27</v>
@@ -9936,13 +9936,13 @@
     </row>
     <row r="203" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A203" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="B203" s="32" t="s">
         <v>671</v>
       </c>
-      <c r="B203" s="32" t="s">
+      <c r="C203" s="25" t="s">
         <v>672</v>
-      </c>
-      <c r="C203" s="25" t="s">
-        <v>673</v>
       </c>
       <c r="D203" s="25" t="s">
         <v>28</v>
@@ -9959,13 +9959,13 @@
     </row>
     <row r="204" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A204" s="25" t="s">
+        <v>673</v>
+      </c>
+      <c r="B204" s="32" t="s">
         <v>674</v>
       </c>
-      <c r="B204" s="32" t="s">
+      <c r="C204" s="25" t="s">
         <v>675</v>
-      </c>
-      <c r="C204" s="25" t="s">
-        <v>676</v>
       </c>
       <c r="D204" s="25" t="s">
         <v>28</v>
@@ -9982,13 +9982,13 @@
     </row>
     <row r="205" spans="1:19" ht="170" x14ac:dyDescent="0.2">
       <c r="A205" s="25" t="s">
+        <v>676</v>
+      </c>
+      <c r="B205" s="32" t="s">
         <v>677</v>
       </c>
-      <c r="B205" s="32" t="s">
+      <c r="C205" s="25" t="s">
         <v>678</v>
-      </c>
-      <c r="C205" s="25" t="s">
-        <v>679</v>
       </c>
       <c r="D205" s="25" t="s">
         <v>27</v>
@@ -10005,13 +10005,13 @@
     </row>
     <row r="206" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A206" s="25" t="s">
+        <v>679</v>
+      </c>
+      <c r="B206" s="32" t="s">
         <v>680</v>
       </c>
-      <c r="B206" s="32" t="s">
+      <c r="C206" s="25" t="s">
         <v>681</v>
-      </c>
-      <c r="C206" s="25" t="s">
-        <v>682</v>
       </c>
       <c r="D206" s="25" t="s">
         <v>27</v>
@@ -10028,13 +10028,13 @@
     </row>
     <row r="207" spans="1:19" ht="170" x14ac:dyDescent="0.2">
       <c r="A207" s="25" t="s">
+        <v>682</v>
+      </c>
+      <c r="B207" s="32" t="s">
         <v>683</v>
       </c>
-      <c r="B207" s="32" t="s">
+      <c r="C207" s="25" t="s">
         <v>684</v>
-      </c>
-      <c r="C207" s="25" t="s">
-        <v>685</v>
       </c>
       <c r="D207" s="25" t="s">
         <v>27</v>
@@ -10051,13 +10051,13 @@
     </row>
     <row r="208" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A208" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="B208" s="32" t="s">
         <v>686</v>
       </c>
-      <c r="B208" s="32" t="s">
-        <v>687</v>
-      </c>
       <c r="C208" s="25" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D208" s="25" t="s">
         <v>27</v>
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="P208" s="27" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="R208" s="27" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="S208" s="27" t="s">
         <v>68</v>
@@ -10080,10 +10080,10 @@
     </row>
     <row r="209" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A209" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="B209" s="32" t="s">
         <v>690</v>
-      </c>
-      <c r="B209" s="32" t="s">
-        <v>691</v>
       </c>
       <c r="C209" s="25" t="s">
         <v>78</v>
@@ -10103,13 +10103,13 @@
     </row>
     <row r="210" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A210" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="B210" s="32" t="s">
         <v>692</v>
       </c>
-      <c r="B210" s="32" t="s">
-        <v>693</v>
-      </c>
       <c r="C210" s="25" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D210" s="25" t="s">
         <v>27</v>
@@ -10121,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="P210" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="R210" s="27" t="s">
         <v>89</v>
@@ -10129,13 +10129,13 @@
     </row>
     <row r="211" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A211" s="25" t="s">
+        <v>695</v>
+      </c>
+      <c r="B211" s="32" t="s">
         <v>696</v>
       </c>
-      <c r="B211" s="32" t="s">
+      <c r="C211" s="25" t="s">
         <v>697</v>
-      </c>
-      <c r="C211" s="25" t="s">
-        <v>698</v>
       </c>
       <c r="D211" s="25" t="s">
         <v>27</v>
@@ -10153,18 +10153,18 @@
         <v>90</v>
       </c>
       <c r="S211" s="27" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="212" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A212" s="25" t="s">
+        <v>698</v>
+      </c>
+      <c r="B212" s="32" t="s">
         <v>699</v>
       </c>
-      <c r="B212" s="32" t="s">
+      <c r="C212" s="25" t="s">
         <v>700</v>
-      </c>
-      <c r="C212" s="25" t="s">
-        <v>701</v>
       </c>
       <c r="D212" s="25" t="s">
         <v>26</v>
@@ -10181,13 +10181,13 @@
     </row>
     <row r="213" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A213" s="25" t="s">
+        <v>701</v>
+      </c>
+      <c r="B213" s="32" t="s">
         <v>702</v>
       </c>
-      <c r="B213" s="32" t="s">
+      <c r="C213" s="25" t="s">
         <v>703</v>
-      </c>
-      <c r="C213" s="25" t="s">
-        <v>704</v>
       </c>
       <c r="D213" s="25" t="s">
         <v>28</v>
@@ -10204,13 +10204,13 @@
     </row>
     <row r="214" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A214" s="25" t="s">
+        <v>704</v>
+      </c>
+      <c r="B214" s="32" t="s">
         <v>705</v>
       </c>
-      <c r="B214" s="32" t="s">
+      <c r="C214" s="25" t="s">
         <v>706</v>
-      </c>
-      <c r="C214" s="25" t="s">
-        <v>707</v>
       </c>
       <c r="D214" s="25" t="s">
         <v>27</v>
@@ -10227,13 +10227,13 @@
     </row>
     <row r="215" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A215" s="25" t="s">
+        <v>707</v>
+      </c>
+      <c r="B215" s="32" t="s">
         <v>708</v>
       </c>
-      <c r="B215" s="32" t="s">
+      <c r="C215" s="25" t="s">
         <v>709</v>
-      </c>
-      <c r="C215" s="25" t="s">
-        <v>710</v>
       </c>
       <c r="D215" s="25" t="s">
         <v>28</v>
@@ -10250,13 +10250,13 @@
     </row>
     <row r="216" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A216" s="25" t="s">
+        <v>710</v>
+      </c>
+      <c r="B216" s="32" t="s">
         <v>711</v>
       </c>
-      <c r="B216" s="32" t="s">
+      <c r="C216" s="25" t="s">
         <v>712</v>
-      </c>
-      <c r="C216" s="25" t="s">
-        <v>713</v>
       </c>
       <c r="D216" s="25" t="s">
         <v>28</v>
@@ -10273,10 +10273,10 @@
     </row>
     <row r="217" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A217" s="25" t="s">
+        <v>713</v>
+      </c>
+      <c r="B217" s="32" t="s">
         <v>714</v>
-      </c>
-      <c r="B217" s="32" t="s">
-        <v>715</v>
       </c>
       <c r="C217" s="25" t="s">
         <v>79</v>
@@ -10296,13 +10296,13 @@
     </row>
     <row r="218" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A218" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="B218" s="32" t="s">
         <v>716</v>
       </c>
-      <c r="B218" s="32" t="s">
+      <c r="C218" s="25" t="s">
         <v>717</v>
-      </c>
-      <c r="C218" s="25" t="s">
-        <v>718</v>
       </c>
       <c r="D218" s="25" t="s">
         <v>27</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="219" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A219" s="25" t="s">
+        <v>718</v>
+      </c>
+      <c r="B219" s="32" t="s">
         <v>719</v>
-      </c>
-      <c r="B219" s="32" t="s">
-        <v>720</v>
       </c>
       <c r="C219" s="25" t="s">
         <v>80</v>
@@ -10342,13 +10342,13 @@
     </row>
     <row r="220" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A220" s="25" t="s">
+        <v>720</v>
+      </c>
+      <c r="B220" s="32" t="s">
         <v>721</v>
       </c>
-      <c r="B220" s="32" t="s">
+      <c r="C220" s="25" t="s">
         <v>722</v>
-      </c>
-      <c r="C220" s="25" t="s">
-        <v>723</v>
       </c>
       <c r="D220" s="25" t="s">
         <v>27</v>
@@ -10365,13 +10365,13 @@
     </row>
     <row r="221" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A221" s="25" t="s">
+        <v>723</v>
+      </c>
+      <c r="B221" s="32" t="s">
         <v>724</v>
       </c>
-      <c r="B221" s="32" t="s">
+      <c r="C221" s="25" t="s">
         <v>725</v>
-      </c>
-      <c r="C221" s="25" t="s">
-        <v>726</v>
       </c>
       <c r="D221" s="25" t="s">
         <v>30</v>
@@ -10388,13 +10388,13 @@
     </row>
     <row r="222" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A222" s="25" t="s">
+        <v>726</v>
+      </c>
+      <c r="B222" s="32" t="s">
         <v>727</v>
       </c>
-      <c r="B222" s="32" t="s">
+      <c r="C222" s="25" t="s">
         <v>728</v>
-      </c>
-      <c r="C222" s="25" t="s">
-        <v>729</v>
       </c>
       <c r="D222" s="25" t="s">
         <v>26</v>
@@ -10411,13 +10411,13 @@
     </row>
     <row r="223" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A223" s="25" t="s">
+        <v>729</v>
+      </c>
+      <c r="B223" s="32" t="s">
         <v>730</v>
       </c>
-      <c r="B223" s="32" t="s">
+      <c r="C223" s="25" t="s">
         <v>731</v>
-      </c>
-      <c r="C223" s="25" t="s">
-        <v>732</v>
       </c>
       <c r="D223" s="25" t="s">
         <v>27</v>
@@ -10432,15 +10432,15 @@
         <v>93</v>
       </c>
       <c r="R223" s="27" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="224" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A224" s="25" t="s">
+        <v>732</v>
+      </c>
+      <c r="B224" s="32" t="s">
         <v>733</v>
-      </c>
-      <c r="B224" s="32" t="s">
-        <v>734</v>
       </c>
       <c r="C224" s="25" t="s">
         <v>81</v>
@@ -10460,13 +10460,13 @@
     </row>
     <row r="225" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A225" s="25" t="s">
+        <v>734</v>
+      </c>
+      <c r="B225" s="32" t="s">
         <v>735</v>
       </c>
-      <c r="B225" s="32" t="s">
+      <c r="C225" s="25" t="s">
         <v>736</v>
-      </c>
-      <c r="C225" s="25" t="s">
-        <v>737</v>
       </c>
       <c r="D225" s="25" t="s">
         <v>28</v>
@@ -10483,13 +10483,13 @@
     </row>
     <row r="226" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A226" s="25" t="s">
+        <v>737</v>
+      </c>
+      <c r="B226" s="32" t="s">
         <v>738</v>
       </c>
-      <c r="B226" s="32" t="s">
+      <c r="C226" s="25" t="s">
         <v>739</v>
-      </c>
-      <c r="C226" s="25" t="s">
-        <v>740</v>
       </c>
       <c r="D226" s="25" t="s">
         <v>28</v>
@@ -10501,18 +10501,18 @@
         <v>0</v>
       </c>
       <c r="P226" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="227" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A227" s="25" t="s">
+        <v>740</v>
+      </c>
+      <c r="B227" s="32" t="s">
         <v>741</v>
       </c>
-      <c r="B227" s="32" t="s">
+      <c r="C227" s="25" t="s">
         <v>742</v>
-      </c>
-      <c r="C227" s="25" t="s">
-        <v>743</v>
       </c>
       <c r="D227" s="25" t="s">
         <v>27</v>
@@ -10529,13 +10529,13 @@
     </row>
     <row r="228" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A228" s="25" t="s">
+        <v>743</v>
+      </c>
+      <c r="B228" s="32" t="s">
         <v>744</v>
       </c>
-      <c r="B228" s="32" t="s">
+      <c r="C228" s="25" t="s">
         <v>745</v>
-      </c>
-      <c r="C228" s="25" t="s">
-        <v>746</v>
       </c>
       <c r="D228" s="25" t="s">
         <v>26</v>
@@ -10552,13 +10552,13 @@
     </row>
     <row r="229" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A229" s="25" t="s">
+        <v>746</v>
+      </c>
+      <c r="B229" s="32" t="s">
         <v>747</v>
       </c>
-      <c r="B229" s="32" t="s">
+      <c r="C229" s="25" t="s">
         <v>748</v>
-      </c>
-      <c r="C229" s="25" t="s">
-        <v>749</v>
       </c>
       <c r="D229" s="25" t="s">
         <v>27</v>
@@ -10573,18 +10573,18 @@
         <v>93</v>
       </c>
       <c r="R229" s="27" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="230" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A230" s="25" t="s">
+        <v>749</v>
+      </c>
+      <c r="B230" s="32" t="s">
         <v>750</v>
       </c>
-      <c r="B230" s="32" t="s">
+      <c r="C230" s="25" t="s">
         <v>751</v>
-      </c>
-      <c r="C230" s="25" t="s">
-        <v>752</v>
       </c>
       <c r="D230" s="25" t="s">
         <v>26</v>
@@ -10601,13 +10601,13 @@
     </row>
     <row r="231" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A231" s="25" t="s">
+        <v>752</v>
+      </c>
+      <c r="B231" s="32" t="s">
         <v>753</v>
       </c>
-      <c r="B231" s="32" t="s">
+      <c r="C231" s="25" t="s">
         <v>754</v>
-      </c>
-      <c r="C231" s="25" t="s">
-        <v>755</v>
       </c>
       <c r="D231" s="25" t="s">
         <v>30</v>
@@ -10624,13 +10624,13 @@
     </row>
     <row r="232" spans="1:19" ht="119" x14ac:dyDescent="0.2">
       <c r="A232" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="B232" s="32" t="s">
         <v>756</v>
       </c>
-      <c r="B232" s="32" t="s">
+      <c r="C232" s="25" t="s">
         <v>757</v>
-      </c>
-      <c r="C232" s="25" t="s">
-        <v>758</v>
       </c>
       <c r="D232" s="25" t="s">
         <v>29</v>
@@ -10647,13 +10647,13 @@
     </row>
     <row r="233" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A233" s="25" t="s">
+        <v>758</v>
+      </c>
+      <c r="B233" s="32" t="s">
         <v>759</v>
       </c>
-      <c r="B233" s="32" t="s">
+      <c r="C233" s="25" t="s">
         <v>760</v>
-      </c>
-      <c r="C233" s="25" t="s">
-        <v>761</v>
       </c>
       <c r="D233" s="25" t="s">
         <v>27</v>
@@ -10670,13 +10670,13 @@
     </row>
     <row r="234" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A234" s="25" t="s">
+        <v>761</v>
+      </c>
+      <c r="B234" s="32" t="s">
         <v>762</v>
       </c>
-      <c r="B234" s="32" t="s">
+      <c r="C234" s="25" t="s">
         <v>763</v>
-      </c>
-      <c r="C234" s="25" t="s">
-        <v>764</v>
       </c>
       <c r="D234" s="25" t="s">
         <v>27</v>
@@ -10693,13 +10693,13 @@
     </row>
     <row r="235" spans="1:19" ht="204" x14ac:dyDescent="0.2">
       <c r="A235" s="25" t="s">
+        <v>764</v>
+      </c>
+      <c r="B235" s="32" t="s">
         <v>765</v>
       </c>
-      <c r="B235" s="32" t="s">
-        <v>766</v>
-      </c>
       <c r="C235" s="25" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D235" s="25" t="s">
         <v>27</v>
@@ -10719,13 +10719,13 @@
     </row>
     <row r="236" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A236" s="25" t="s">
+        <v>766</v>
+      </c>
+      <c r="B236" s="32" t="s">
         <v>767</v>
       </c>
-      <c r="B236" s="32" t="s">
+      <c r="C236" s="25" t="s">
         <v>768</v>
-      </c>
-      <c r="C236" s="25" t="s">
-        <v>769</v>
       </c>
       <c r="D236" s="25" t="s">
         <v>27</v>
@@ -10740,7 +10740,7 @@
         <v>93</v>
       </c>
       <c r="R236" s="27" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="S236" s="27" t="s">
         <v>68</v>
@@ -10748,13 +10748,13 @@
     </row>
     <row r="237" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A237" s="25" t="s">
+        <v>769</v>
+      </c>
+      <c r="B237" s="32" t="s">
         <v>770</v>
       </c>
-      <c r="B237" s="32" t="s">
+      <c r="C237" s="25" t="s">
         <v>771</v>
-      </c>
-      <c r="C237" s="25" t="s">
-        <v>772</v>
       </c>
       <c r="D237" s="25" t="s">
         <v>28</v>
@@ -10771,13 +10771,13 @@
     </row>
     <row r="238" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A238" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="B238" s="32" t="s">
         <v>773</v>
       </c>
-      <c r="B238" s="32" t="s">
+      <c r="C238" s="25" t="s">
         <v>774</v>
-      </c>
-      <c r="C238" s="25" t="s">
-        <v>775</v>
       </c>
       <c r="D238" s="25" t="s">
         <v>27</v>
@@ -10792,18 +10792,18 @@
         <v>93</v>
       </c>
       <c r="R238" s="27" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="239" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A239" s="25" t="s">
+        <v>775</v>
+      </c>
+      <c r="B239" s="32" t="s">
         <v>776</v>
       </c>
-      <c r="B239" s="32" t="s">
+      <c r="C239" s="25" t="s">
         <v>777</v>
-      </c>
-      <c r="C239" s="25" t="s">
-        <v>778</v>
       </c>
       <c r="D239" s="25" t="s">
         <v>27</v>
@@ -10820,13 +10820,13 @@
     </row>
     <row r="240" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A240" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="B240" s="32" t="s">
         <v>779</v>
       </c>
-      <c r="B240" s="32" t="s">
+      <c r="C240" s="25" t="s">
         <v>780</v>
-      </c>
-      <c r="C240" s="25" t="s">
-        <v>781</v>
       </c>
       <c r="D240" s="25" t="s">
         <v>30</v>
@@ -10838,18 +10838,18 @@
         <v>0</v>
       </c>
       <c r="P240" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="241" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A241" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="B241" s="32" t="s">
         <v>782</v>
       </c>
-      <c r="B241" s="32" t="s">
+      <c r="C241" s="25" t="s">
         <v>783</v>
-      </c>
-      <c r="C241" s="25" t="s">
-        <v>784</v>
       </c>
       <c r="D241" s="25" t="s">
         <v>27</v>
@@ -10869,13 +10869,13 @@
     </row>
     <row r="242" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A242" s="25" t="s">
+        <v>784</v>
+      </c>
+      <c r="B242" s="32" t="s">
         <v>785</v>
       </c>
-      <c r="B242" s="32" t="s">
+      <c r="C242" s="25" t="s">
         <v>786</v>
-      </c>
-      <c r="C242" s="25" t="s">
-        <v>787</v>
       </c>
       <c r="D242" s="25" t="s">
         <v>28</v>
@@ -10892,13 +10892,13 @@
     </row>
     <row r="243" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A243" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="B243" s="32" t="s">
         <v>788</v>
       </c>
-      <c r="B243" s="32" t="s">
+      <c r="C243" s="25" t="s">
         <v>789</v>
-      </c>
-      <c r="C243" s="25" t="s">
-        <v>790</v>
       </c>
       <c r="D243" s="25" t="s">
         <v>29</v>
@@ -12319,7 +12319,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -12381,15 +12381,15 @@
         <v>45</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="153" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B14" s="42" t="s">
         <v>793</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -12527,28 +12527,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -12802,33 +12780,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45EEC221-F5CD-4DEF-B390-EE14E23A8785}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12846,4 +12820,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>